--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="139">
   <si>
     <t>Allocation</t>
   </si>
@@ -149,9 +149,6 @@
     <t>Resent of Title Fetch - SmartPAY</t>
   </si>
   <si>
-    <t>Status Update SmartPAY</t>
-  </si>
-  <si>
     <t>SOW finalized, FSD received, Under UAT</t>
   </si>
   <si>
@@ -185,9 +182,6 @@
     <t>SIEM Intergration</t>
   </si>
   <si>
-    <t>SWAP</t>
-  </si>
-  <si>
     <t>Scoping Done, SIT in process by Paysys.</t>
   </si>
   <si>
@@ -215,9 +209,6 @@
     <t>Requirement shared with CRPL, SOW finalizaed, FSD finalized, under development</t>
   </si>
   <si>
-    <t>Encryption of Bulk Account upload</t>
-  </si>
-  <si>
     <t>SOW finalized, FSD received . AES encrption required</t>
   </si>
   <si>
@@ -236,9 +227,6 @@
     <t>Allow to collect advance payment against PTCL bill, SOW rasied and shared to OPG for review</t>
   </si>
   <si>
-    <t>GBM</t>
-  </si>
-  <si>
     <t>Revised FSd required from CRPL</t>
   </si>
   <si>
@@ -290,9 +278,6 @@
     <t>Balance Inquiry Length Enhancement</t>
   </si>
   <si>
-    <t>QR Upload</t>
-  </si>
-  <si>
     <t>RAAST/RTGS DMS</t>
   </si>
   <si>
@@ -374,9 +359,6 @@
     <t>BAU</t>
   </si>
   <si>
-    <t xml:space="preserve">File upload via Email /SFTP </t>
-  </si>
-  <si>
     <t>SOW finalizated, FSD received, UAT Done. Production deployment and implenentaiton required, Under IS review, CMC approved.</t>
   </si>
   <si>
@@ -410,9 +392,6 @@
     <t>Raat OTC</t>
   </si>
   <si>
-    <t>Control Gap</t>
-  </si>
-  <si>
     <t>Data Analytics</t>
   </si>
   <si>
@@ -434,7 +413,34 @@
     <t>Payments</t>
   </si>
   <si>
-    <t>IBFT &amp; UBPS Workflow</t>
+    <t>SWAPS</t>
+  </si>
+  <si>
+    <t>GBMS</t>
+  </si>
+  <si>
+    <t>Control Gap - UBCS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payment File upload via Email /SFTP </t>
+  </si>
+  <si>
+    <t>IBFT &amp; UBPS Workflow Change</t>
+  </si>
+  <si>
+    <t>Saad / Adnan</t>
+  </si>
+  <si>
+    <t>Afzal / Adnan</t>
+  </si>
+  <si>
+    <t>Raast QR Upload</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status Update Payment </t>
+  </si>
+  <si>
+    <t>Encryption of Bulk Account upload - Is Issue</t>
   </si>
 </sst>
 </file>
@@ -1321,10 +1327,10 @@
         <v>9</v>
       </c>
       <c r="E2" s="45" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F2" s="46" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1341,10 +1347,10 @@
         <v>10</v>
       </c>
       <c r="E3" s="45" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F3" s="46" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1361,7 +1367,7 @@
         <v>11</v>
       </c>
       <c r="E4" s="45" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F4" s="46" t="s">
         <v>12</v>
@@ -1381,7 +1387,7 @@
         <v>13</v>
       </c>
       <c r="E5" s="45" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F5" s="46" t="s">
         <v>14</v>
@@ -1398,13 +1404,13 @@
         <v>19</v>
       </c>
       <c r="D6" s="44" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="E6" s="45" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1415,13 +1421,13 @@
         <v>7</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D7" s="44" t="s">
         <v>16</v>
       </c>
       <c r="E7" s="45" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F7" s="46" t="s">
         <v>17</v>
@@ -1441,10 +1447,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="45" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F8" s="46" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1472,19 +1478,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C10" s="20" t="s">
         <v>8</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="E10" s="45" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1498,13 +1504,13 @@
         <v>19</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1538,13 +1544,13 @@
         <v>19</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F13" s="49" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1578,13 +1584,13 @@
         <v>8</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>63</v>
+        <v>138</v>
       </c>
       <c r="E15" s="45" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F15" s="46" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1595,16 +1601,16 @@
         <v>7</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="E16" s="45" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1624,27 +1630,27 @@
         <v>46176</v>
       </c>
       <c r="F17" s="46" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="43" t="s">
-        <v>6</v>
+        <v>135</v>
       </c>
       <c r="B18" s="50" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="E18" s="45" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1718,13 +1724,13 @@
         <v>15</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1735,16 +1741,16 @@
         <v>7</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1758,13 +1764,13 @@
         <v>19</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E24" s="3">
         <v>46125</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1775,16 +1781,16 @@
         <v>28</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E25" s="36" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1798,13 +1804,13 @@
         <v>8</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="E26" s="36" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1815,16 +1821,16 @@
         <v>28</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E27" s="36" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1835,16 +1841,16 @@
         <v>28</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>88</v>
+        <v>136</v>
       </c>
       <c r="E28" s="36" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -1855,16 +1861,16 @@
         <v>28</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="E29" s="36" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -1875,16 +1881,16 @@
         <v>28</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>39</v>
       </c>
       <c r="E30" s="36" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1904,7 +1910,7 @@
         <v>46276</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1918,13 +1924,13 @@
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E32" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="F32" s="9" t="s">
         <v>41</v>
-      </c>
-      <c r="E32" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1938,13 +1944,13 @@
         <v>19</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E33" s="3">
         <v>46161</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1958,13 +1964,13 @@
         <v>19</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E34" s="3">
         <v>46147</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1978,13 +1984,13 @@
         <v>19</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E35" s="3">
         <v>46122</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1995,16 +2001,16 @@
         <v>28</v>
       </c>
       <c r="C36" s="40" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D36" s="41" t="s">
+        <v>120</v>
+      </c>
+      <c r="E36" s="45" t="s">
+        <v>110</v>
+      </c>
+      <c r="F36" s="42" t="s">
         <v>126</v>
-      </c>
-      <c r="E36" s="45" t="s">
-        <v>115</v>
-      </c>
-      <c r="F36" s="42" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2015,41 +2021,41 @@
         <v>7</v>
       </c>
       <c r="C37" s="40" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D37" s="41" t="s">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E37" s="45" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F37" s="42" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E38" s="36" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>28</v>
@@ -2058,18 +2064,18 @@
         <v>15</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E39" s="36" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>7</v>
@@ -2078,18 +2084,18 @@
         <v>8</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>53</v>
+        <v>129</v>
       </c>
       <c r="E40" s="36" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>7</v>
@@ -2098,38 +2104,38 @@
         <v>19</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E41" s="6">
         <v>46059</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E42" s="6">
         <v>46181</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>7</v>
@@ -2138,38 +2144,38 @@
         <v>19</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="E43" s="6">
         <v>46227</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E44" s="36" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>28</v>
@@ -2178,18 +2184,18 @@
         <v>19</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E45" s="6">
         <v>46161</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>28</v>
@@ -2198,58 +2204,58 @@
         <v>8</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="E46" s="36" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E47" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="F47" s="10" t="s">
         <v>114</v>
-      </c>
-      <c r="F47" s="10" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>70</v>
+        <v>130</v>
       </c>
       <c r="E48" s="36" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>28</v>
@@ -2258,158 +2264,158 @@
         <v>19</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E49" s="6">
         <v>46181</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="E50" s="36" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>81</v>
+        <v>134</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="E51" s="36" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="E52" s="36" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>28</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E53" s="36" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="23" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="E54" s="36" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F54" s="22" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="19" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D55" s="35" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="E55" s="51" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F55" s="35" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="C56" s="19" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D56" s="35" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E56" s="51" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F56" s="35" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B57" s="27" t="s">
         <v>7</v>
@@ -2418,38 +2424,38 @@
         <v>8</v>
       </c>
       <c r="D57" s="28" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E57" s="36" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F57" s="29" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="26" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C58" s="27" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D58" s="28" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="E58" s="52" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F58" s="29" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B59" s="27" t="s">
         <v>29</v>
@@ -2461,7 +2467,7 @@
         <v>34</v>
       </c>
       <c r="E59" s="36" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="F59" s="29" t="s">
         <v>35</v>
@@ -2469,42 +2475,42 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="26" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B60" s="27" t="s">
         <v>7</v>
       </c>
       <c r="C60" s="27" t="s">
+        <v>48</v>
+      </c>
+      <c r="D60" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="E60" s="36" t="s">
+        <v>109</v>
+      </c>
+      <c r="F60" s="29" t="s">
         <v>49</v>
-      </c>
-      <c r="D60" s="28" t="s">
-        <v>92</v>
-      </c>
-      <c r="E60" s="36" t="s">
-        <v>114</v>
-      </c>
-      <c r="F60" s="29" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="B61" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="C61" s="27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D61" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="B61" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="C61" s="27" t="s">
-        <v>115</v>
-      </c>
-      <c r="D61" s="28" t="s">
-        <v>76</v>
-      </c>
       <c r="E61" s="52" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="F61" s="29" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -1421,7 +1421,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="D7" s="44" t="s">
         <v>16</v>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="137">
   <si>
     <t>Allocation</t>
   </si>
@@ -62,9 +62,6 @@
     <t>NTC - National Telecommunication Centre</t>
   </si>
   <si>
-    <t>API documented raised to vendor and initial meeting done , agreement signoff. Connectivity done</t>
-  </si>
-  <si>
     <t>Pak Austria</t>
   </si>
   <si>
@@ -119,15 +116,9 @@
     <t>PSW AD Changes</t>
   </si>
   <si>
-    <t>UAT DONE, IS REVIEW DONE, CMC Approved, Deployment on Friday</t>
-  </si>
-  <si>
     <t>PSW PCS</t>
   </si>
   <si>
-    <t>UAT DONE, Under IS Review</t>
-  </si>
-  <si>
     <t>PSW Price Verification</t>
   </si>
   <si>
@@ -137,9 +128,6 @@
     <t>RAAST TTC</t>
   </si>
   <si>
-    <t>Addition and update on RAAST TTC code</t>
-  </si>
-  <si>
     <t>Mubashir</t>
   </si>
   <si>
@@ -173,9 +161,6 @@
     <t>Under Scoping</t>
   </si>
   <si>
-    <t>BRD shared with IT.</t>
-  </si>
-  <si>
     <t>Outward Clearing</t>
   </si>
   <si>
@@ -200,21 +185,9 @@
     <t>RF Account on SmartPAY</t>
   </si>
   <si>
-    <t>UAT Done. Shared with IT, UAT Done. Confirmation from Business team received. Deployment done</t>
-  </si>
-  <si>
     <t>Tokinization on SmartPAY</t>
   </si>
   <si>
-    <t>Requirement shared with CRPL, SOW finalizaed, FSD finalized, under development</t>
-  </si>
-  <si>
-    <t>SOW finalized, FSD received . AES encrption required</t>
-  </si>
-  <si>
-    <t>BRD raised with CRPL, SOW finalized, FSD and efforts required</t>
-  </si>
-  <si>
     <t>Host to Host intergration for Payments</t>
   </si>
   <si>
@@ -224,12 +197,6 @@
     <t>PTCL Advance Payment</t>
   </si>
   <si>
-    <t>Allow to collect advance payment against PTCL bill, SOW rasied and shared to OPG for review</t>
-  </si>
-  <si>
-    <t>Revised FSd required from CRPL</t>
-  </si>
-  <si>
     <t>Adnan Younis</t>
   </si>
   <si>
@@ -368,9 +335,6 @@
     <t>UAT DONE, Circular pending, Live</t>
   </si>
   <si>
-    <t>Under scoping, CRPL and PAYSYS meeting done, SOW required</t>
-  </si>
-  <si>
     <t>Under scoping</t>
   </si>
   <si>
@@ -428,9 +392,6 @@
     <t>IBFT &amp; UBPS Workflow Change</t>
   </si>
   <si>
-    <t>Saad / Adnan</t>
-  </si>
-  <si>
     <t>Afzal / Adnan</t>
   </si>
   <si>
@@ -441,6 +402,39 @@
   </si>
   <si>
     <t>Encryption of Bulk Account upload - Is Issue</t>
+  </si>
+  <si>
+    <t>SOW and FSD approved. Currently under QA; will be moved to UAT after QA approval.</t>
+  </si>
+  <si>
+    <t>CRPL is working on it and will share an update accordingly.</t>
+  </si>
+  <si>
+    <t>SOW and FSD approved. CRPL will provide the UAT patch.</t>
+  </si>
+  <si>
+    <t>UAT DONE, Under IS Review,Live.</t>
+  </si>
+  <si>
+    <t>Addition and update on RAAST TTC code, Live</t>
+  </si>
+  <si>
+    <t>UAT DONE, IS REVIEW DONE, CMC Approved, Live</t>
+  </si>
+  <si>
+    <t>Requirement shared with CRPL, SOW finalizaed, FSD finalized, currently under QA and will be moved to UAT upon approval.</t>
+  </si>
+  <si>
+    <t>UAT Done. Shared with IT, UAT Done. Confirmation from Business team received. Deployment done,Live</t>
+  </si>
+  <si>
+    <t>Under scoping, CRPL and PAYSYS meeting done, SOW required from Paysys</t>
+  </si>
+  <si>
+    <t>Revised FSD is required from CRPL. A physical meeting between CRPL, OPG, and DBG will be held this week to discuss the FSD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BRD raised with CRPL, SOW finalized, FSD and efforts required, under development </t>
   </si>
 </sst>
 </file>
@@ -1321,16 +1315,16 @@
         <v>7</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D2" s="44" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="45" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F2" s="46" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1341,16 +1335,16 @@
         <v>7</v>
       </c>
       <c r="C3" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" s="44" t="s">
         <v>10</v>
       </c>
       <c r="E3" s="45" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F3" s="46" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1361,16 +1355,16 @@
         <v>7</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D4" s="44" t="s">
         <v>11</v>
       </c>
       <c r="E4" s="45" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F4" s="46" t="s">
-        <v>12</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1384,13 +1378,13 @@
         <v>8</v>
       </c>
       <c r="D5" s="44" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="F5" s="46" t="s">
         <v>13</v>
-      </c>
-      <c r="E5" s="45" t="s">
-        <v>109</v>
-      </c>
-      <c r="F5" s="46" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1401,16 +1395,16 @@
         <v>7</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" s="44" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="E6" s="45" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F6" s="46" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -1424,13 +1418,13 @@
         <v>8</v>
       </c>
       <c r="D7" s="44" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" s="45" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" s="46" t="s">
         <v>16</v>
-      </c>
-      <c r="E7" s="45" t="s">
-        <v>109</v>
-      </c>
-      <c r="F7" s="46" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -1441,16 +1435,16 @@
         <v>7</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8" s="44" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8" s="45" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F8" s="46" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1461,16 +1455,16 @@
         <v>7</v>
       </c>
       <c r="C9" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D9" s="44" t="s">
         <v>19</v>
-      </c>
-      <c r="D9" s="44" t="s">
-        <v>20</v>
       </c>
       <c r="E9" s="47">
         <v>46218</v>
       </c>
       <c r="F9" s="46" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1478,19 +1472,19 @@
         <v>6</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>97</v>
-      </c>
-      <c r="C10" s="20" t="s">
-        <v>8</v>
+        <v>86</v>
+      </c>
+      <c r="C10" s="50" t="s">
+        <v>82</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="E10" s="45" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F10" s="22" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1501,16 +1495,16 @@
         <v>7</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F11" s="22" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1521,16 +1515,16 @@
         <v>7</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E12" s="47">
         <v>46218</v>
       </c>
       <c r="F12" s="46" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1541,16 +1535,16 @@
         <v>7</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F13" s="49" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1561,16 +1555,16 @@
         <v>7</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E14" s="47">
         <v>46220</v>
       </c>
       <c r="F14" s="46" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.25">
@@ -1584,13 +1578,13 @@
         <v>8</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="E15" s="45" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F15" s="46" t="s">
-        <v>61</v>
+        <v>128</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1601,16 +1595,16 @@
         <v>7</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="E16" s="45" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1621,461 +1615,461 @@
         <v>7</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D17" s="44" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E17" s="47">
         <v>46176</v>
       </c>
       <c r="F17" s="46" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="43" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="B18" s="50" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="E18" s="45" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F18" s="22" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="32" t="s">
         <v>29</v>
-      </c>
-      <c r="C19" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="D19" s="32" t="s">
-        <v>30</v>
       </c>
       <c r="E19" s="33">
         <v>46241</v>
       </c>
       <c r="F19" s="34" t="s">
-        <v>31</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B20" s="31" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C20" s="31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D20" s="32" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E20" s="36">
         <v>46261</v>
       </c>
       <c r="F20" s="34" t="s">
-        <v>33</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B21" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="B21" s="31" t="s">
-        <v>28</v>
-      </c>
       <c r="C21" s="31" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D21" s="32" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="E21" s="33">
         <v>46227</v>
       </c>
       <c r="F21" s="34" t="s">
-        <v>37</v>
+        <v>130</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B22" s="16" t="s">
         <v>7</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="E22" s="36" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B23" s="16" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="E23" s="36" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="E24" s="3">
         <v>46125</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="E25" s="36" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="24" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B26" s="25" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C26" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="E26" s="36" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F26" s="18" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="E27" s="36" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="E28" s="36" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B29" s="16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C29" s="16" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="E29" s="36" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F29" s="18" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E30" s="36" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E31" s="36">
         <v>46276</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="E33" s="3">
         <v>46161</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="E34" s="3">
         <v>46147</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="E35" s="3">
         <v>46122</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="39" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B36" s="40" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C36" s="40" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D36" s="41" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="E36" s="45" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F36" s="42" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="39" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B37" s="40" t="s">
         <v>7</v>
       </c>
       <c r="C37" s="40" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D37" s="41" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E37" s="45" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F37" s="42" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="8" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E38" s="36" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F38" s="10" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="8" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="E39" s="36" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F39" s="10" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="8" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>7</v>
@@ -2084,338 +2078,338 @@
         <v>8</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="E40" s="36" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E41" s="6">
         <v>46059</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E42" s="6">
         <v>46181</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D43" s="5" t="s">
         <v>77</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>88</v>
       </c>
       <c r="E43" s="6">
         <v>46227</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="E44" s="36" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>60</v>
+        <v>132</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E45" s="6">
         <v>46161</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>58</v>
+        <v>133</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="E46" s="36" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="E47" s="36" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="E48" s="36" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>67</v>
+        <v>135</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="E49" s="6">
         <v>46181</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="E50" s="36" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>134</v>
+        <v>66</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="E51" s="36" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="E52" s="36" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="E53" s="36" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="23" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B54" s="20" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="C54" s="20" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D54" s="21" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E54" s="36" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F54" s="22" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="19" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B55" s="19" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="C55" s="19" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D55" s="35" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="E55" s="51" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F55" s="35" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B56" s="19" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="C56" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="D56" s="35" t="s">
         <v>110</v>
       </c>
-      <c r="D56" s="35" t="s">
-        <v>122</v>
-      </c>
       <c r="E56" s="51" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F56" s="35" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B57" s="27" t="s">
         <v>7</v>
@@ -2424,93 +2418,93 @@
         <v>8</v>
       </c>
       <c r="D57" s="28" t="s">
-        <v>65</v>
+        <v>56</v>
       </c>
       <c r="E57" s="36" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F57" s="29" t="s">
-        <v>66</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="26" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="C58" s="27" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D58" s="28" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="E58" s="52" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F58" s="29" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C59" s="27" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="28" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E59" s="36" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F59" s="29" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="26" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B60" s="27" t="s">
         <v>7</v>
       </c>
       <c r="C60" s="27" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="D60" s="28" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="E60" s="36" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F60" s="29" t="s">
-        <v>49</v>
+        <v>127</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="26" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="C61" s="27" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="D61" s="28" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="E61" s="52" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F61" s="29" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -203,9 +203,6 @@
     <t xml:space="preserve">R22 Upgrade </t>
   </si>
   <si>
-    <t>The agreement is nearing finalization.</t>
-  </si>
-  <si>
     <t>This matter is currently pending review by legal counsel.</t>
   </si>
   <si>
@@ -311,12 +308,6 @@
     <t>PASSPORT FEE MIS reporting and QR</t>
   </si>
   <si>
-    <t>Under development</t>
-  </si>
-  <si>
-    <t>Purpose of payment in CORE naarration (IBT)</t>
-  </si>
-  <si>
     <t>SOW finalized, FSD received, Under UAT,Under Is review. For CMC approval</t>
   </si>
   <si>
@@ -341,9 +332,6 @@
     <t>Under Scoping.BRD Shared with crpl</t>
   </si>
   <si>
-    <t>UGDC</t>
-  </si>
-  <si>
     <t xml:space="preserve">Branch collection/ API Billers </t>
   </si>
   <si>
@@ -435,6 +423,18 @@
   </si>
   <si>
     <t xml:space="preserve">BRD raised with CRPL, SOW finalized, FSD and efforts required, under development </t>
+  </si>
+  <si>
+    <t>HR Salary-Purpose IBT</t>
+  </si>
+  <si>
+    <t>Scoping</t>
+  </si>
+  <si>
+    <t>Govt Salaries &amp; Pension (Putty)</t>
+  </si>
+  <si>
+    <t>Scoping.</t>
   </si>
 </sst>
 </file>
@@ -1279,7 +1279,7 @@
   <dimension ref="A1:F61"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="51.85546875" bestFit="1" customWidth="1"/>
@@ -1308,43 +1308,43 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="19" t="s">
+      <c r="A2" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="44" t="s">
-        <v>9</v>
-      </c>
-      <c r="E2" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="F2" s="46" t="s">
-        <v>68</v>
+      <c r="C2" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="E2" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="19" t="s">
+      <c r="A3" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="44" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="F3" s="46" t="s">
-        <v>67</v>
+      <c r="C3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -1361,90 +1361,90 @@
         <v>11</v>
       </c>
       <c r="E4" s="45" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F4" s="46" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="44" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="F5" s="46" t="s">
-        <v>13</v>
+      <c r="A5" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="44" t="s">
-        <v>94</v>
-      </c>
-      <c r="E6" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="F6" s="46" t="s">
-        <v>100</v>
+      <c r="A6" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="F6" s="9" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="F7" s="46" t="s">
-        <v>16</v>
+      <c r="A7" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="F7" s="29" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>18</v>
-      </c>
-      <c r="D8" s="44" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="F8" s="46" t="s">
-        <v>101</v>
+      <c r="A8" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>135</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="F8" s="34" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1458,53 +1458,53 @@
         <v>18</v>
       </c>
       <c r="D9" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="47">
-        <v>46218</v>
+        <v>9</v>
+      </c>
+      <c r="E9" s="45" t="s">
+        <v>95</v>
       </c>
       <c r="F9" s="46" t="s">
-        <v>20</v>
+        <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="48" t="s">
+      <c r="A10" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="20" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" s="50" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>87</v>
+      <c r="B10" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D10" s="44" t="s">
+        <v>10</v>
       </c>
       <c r="E10" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="F10" s="22" t="s">
-        <v>88</v>
+        <v>95</v>
+      </c>
+      <c r="F10" s="46" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>89</v>
+      <c r="C11" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="44" t="s">
+        <v>12</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="F11" s="22" t="s">
-        <v>74</v>
+        <v>95</v>
+      </c>
+      <c r="F11" s="46" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -1518,33 +1518,33 @@
         <v>18</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="E12" s="47">
-        <v>46218</v>
+        <v>93</v>
+      </c>
+      <c r="E12" s="45" t="s">
+        <v>95</v>
       </c>
       <c r="F12" s="46" t="s">
-        <v>22</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>93</v>
+      <c r="C13" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="44" t="s">
+        <v>15</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="F13" s="49" t="s">
-        <v>74</v>
+        <v>95</v>
+      </c>
+      <c r="F13" s="46" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1558,13 +1558,13 @@
         <v>18</v>
       </c>
       <c r="D14" s="44" t="s">
-        <v>23</v>
-      </c>
-      <c r="E14" s="47">
-        <v>46220</v>
+        <v>17</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>95</v>
       </c>
       <c r="F14" s="46" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.25">
@@ -1575,256 +1575,256 @@
         <v>7</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D15" s="44" t="s">
-        <v>125</v>
-      </c>
-      <c r="E15" s="45" t="s">
-        <v>98</v>
+        <v>19</v>
+      </c>
+      <c r="E15" s="47">
+        <v>46218</v>
       </c>
       <c r="F15" s="46" t="s">
-        <v>128</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="43" t="s">
+      <c r="A16" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="50" t="s">
+      <c r="B16" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C16" s="50" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="E16" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="F16" s="22" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="B17" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="D16" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="E16" s="45" t="s">
-        <v>98</v>
-      </c>
-      <c r="F16" s="22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="B17" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="47">
-        <v>46176</v>
-      </c>
-      <c r="F17" s="46" t="s">
-        <v>102</v>
+      <c r="D17" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="E17" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="B18" s="50" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" s="19" t="s">
         <v>7</v>
       </c>
       <c r="C18" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="44" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" s="47">
+        <v>46218</v>
+      </c>
+      <c r="F18" s="46" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="23" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="F19" s="49" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="44" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="47">
+        <v>46220</v>
+      </c>
+      <c r="F20" s="46" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="B21" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="44" t="s">
+        <v>121</v>
+      </c>
+      <c r="E21" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="F21" s="46" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="47">
+        <v>46176</v>
+      </c>
+      <c r="F22" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="D18" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="E18" s="45" t="s">
-        <v>99</v>
-      </c>
-      <c r="F18" s="22" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="30" t="s">
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="B23" s="50" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="E23" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="B24" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="31" t="s">
+      <c r="C24" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D24" s="32" t="s">
         <v>29</v>
       </c>
-      <c r="E19" s="33">
+      <c r="E24" s="33">
         <v>46241</v>
       </c>
-      <c r="F19" s="34" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="30" t="s">
+      <c r="F24" s="34" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="31" t="s">
+      <c r="B25" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C25" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D25" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="E20" s="36">
+      <c r="E25" s="33">
         <v>46261</v>
       </c>
-      <c r="F20" s="34" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="30" t="s">
+      <c r="F25" s="34" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="B21" s="31" t="s">
+      <c r="B26" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="C21" s="31" t="s">
+      <c r="C26" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="32" t="s">
+      <c r="D26" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="E21" s="33">
+      <c r="E26" s="33">
         <v>46227</v>
       </c>
-      <c r="F21" s="34" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
+      <c r="F26" s="34" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B27" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="16" t="s">
+      <c r="C27" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D27" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="F27" s="18" t="s">
         <v>69</v>
-      </c>
-      <c r="E22" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="F22" s="18" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E23" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="F23" s="9" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E24" s="3">
-        <v>46125</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E25" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="E26" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="F26" s="18" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E27" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1832,99 +1832,99 @@
         <v>34</v>
       </c>
       <c r="B28" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C28" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="17" t="s">
-        <v>123</v>
+      <c r="D28" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="E28" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>104</v>
+        <v>95</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="D29" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="E29" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="F29" s="18" t="s">
-        <v>75</v>
+      <c r="C29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E29" s="3">
+        <v>46125</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>35</v>
+      <c r="C30" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>90</v>
       </c>
       <c r="E30" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>97</v>
+        <v>95</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E31" s="36">
-        <v>46276</v>
-      </c>
-      <c r="F31" s="9" t="s">
-        <v>97</v>
+      <c r="C31" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D31" s="17" t="s">
+        <v>119</v>
+      </c>
+      <c r="E31" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>124</v>
+      <c r="C32" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D32" s="17" t="s">
+        <v>103</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="F32" s="9" t="s">
-        <v>37</v>
+        <v>95</v>
+      </c>
+      <c r="F32" s="18" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1935,16 +1935,16 @@
         <v>27</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E33" s="3">
-        <v>46161</v>
+        <v>35</v>
+      </c>
+      <c r="E33" s="36" t="s">
+        <v>95</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>39</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1958,13 +1958,13 @@
         <v>18</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E34" s="3">
-        <v>46147</v>
+        <v>36</v>
+      </c>
+      <c r="E34" s="36">
+        <v>46276</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>41</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1975,161 +1975,161 @@
         <v>27</v>
       </c>
       <c r="C35" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E35" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="F35" s="9" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D36" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E36" s="3">
+        <v>46161</v>
+      </c>
+      <c r="F36" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E37" s="3">
+        <v>46147</v>
+      </c>
+      <c r="F37" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E38" s="3">
         <v>46122</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="F38" s="9" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="39" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="B36" s="40" t="s">
+      <c r="B39" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="C36" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="D36" s="41" t="s">
-        <v>108</v>
-      </c>
-      <c r="E36" s="45" t="s">
-        <v>99</v>
-      </c>
-      <c r="F36" s="42" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="39" t="s">
+      <c r="C39" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="D39" s="41" t="s">
+        <v>104</v>
+      </c>
+      <c r="E39" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="F39" s="42" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="40" t="s">
+      <c r="B40" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="C37" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="D37" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="E37" s="45" t="s">
-        <v>99</v>
-      </c>
-      <c r="F37" s="42" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E38" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="F38" s="10" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E39" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="F39" s="10" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="E40" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="F40" s="10" t="s">
-        <v>47</v>
+      <c r="C40" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="D40" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="E40" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="F40" s="42" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>7</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E41" s="6">
-        <v>46059</v>
+        <v>45</v>
+      </c>
+      <c r="E41" s="36" t="s">
+        <v>95</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E42" s="6">
-        <v>46181</v>
+        <v>46</v>
+      </c>
+      <c r="E42" s="36" t="s">
+        <v>95</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>50</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>7</v>
@@ -2138,293 +2138,293 @@
         <v>18</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="E43" s="6">
-        <v>46227</v>
+        <v>46059</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>51</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>38</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E44" s="36" t="s">
-        <v>98</v>
+        <v>49</v>
+      </c>
+      <c r="E44" s="6">
+        <v>46181</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>132</v>
+        <v>50</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="E45" s="6">
-        <v>46161</v>
+        <v>46227</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>133</v>
+        <v>51</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="E46" s="36" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="E47" s="36" t="s">
-        <v>98</v>
+        <v>52</v>
+      </c>
+      <c r="E47" s="6">
+        <v>46161</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="E48" s="36" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E49" s="6">
-        <v>46181</v>
+        <v>117</v>
+      </c>
+      <c r="E49" s="36" t="s">
+        <v>95</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>81</v>
+        <v>130</v>
       </c>
     </row>
     <row r="50" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>99</v>
+        <v>18</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E50" s="36" t="s">
-        <v>99</v>
+        <v>53</v>
+      </c>
+      <c r="E50" s="6">
+        <v>46181</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>114</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="E51" s="36" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="E52" s="36" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>27</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E53" s="36" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F53" s="10" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="23" t="s">
-        <v>62</v>
-      </c>
-      <c r="B54" s="20" t="s">
+      <c r="A54" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E54" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="F54" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="C55" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D55" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="C54" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="D54" s="21" t="s">
+      <c r="E55" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="F55" s="22" t="s">
         <v>84</v>
-      </c>
-      <c r="E54" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="F54" s="22" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="B55" s="19" t="s">
-        <v>63</v>
-      </c>
-      <c r="C55" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="D55" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="E55" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="F55" s="35" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="B56" s="19" t="s">
+      <c r="C56" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D56" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="E56" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="F56" s="35" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C57" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D57" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="E57" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="F57" s="35" t="s">
         <v>110</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="D56" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="E56" s="51" t="s">
-        <v>99</v>
-      </c>
-      <c r="F56" s="35" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="B57" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="C57" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="E57" s="36" t="s">
-        <v>98</v>
-      </c>
-      <c r="F57" s="29" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -2432,19 +2432,19 @@
         <v>57</v>
       </c>
       <c r="B58" s="27" t="s">
-        <v>58</v>
+        <v>7</v>
       </c>
       <c r="C58" s="27" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="D58" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="E58" s="52" t="s">
-        <v>98</v>
+        <v>56</v>
+      </c>
+      <c r="E58" s="36" t="s">
+        <v>95</v>
       </c>
       <c r="F58" s="29" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2461,7 +2461,7 @@
         <v>31</v>
       </c>
       <c r="E59" s="36" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F59" s="29" t="s">
         <v>32</v>
@@ -2478,13 +2478,13 @@
         <v>44</v>
       </c>
       <c r="D60" s="28" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E60" s="36" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="F60" s="29" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2492,19 +2492,19 @@
         <v>57</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="C61" s="27" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D61" s="28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E61" s="52" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F61" s="29" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="349" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="138">
   <si>
     <t>Allocation</t>
   </si>
@@ -416,12 +416,6 @@
     <t>UAT Done. Shared with IT, UAT Done. Confirmation from Business team received. Deployment done,Live</t>
   </si>
   <si>
-    <t>Under scoping, CRPL and PAYSYS meeting done, SOW required from Paysys</t>
-  </si>
-  <si>
-    <t>Revised FSD is required from CRPL. A physical meeting between CRPL, OPG, and DBG will be held this week to discuss the FSD.</t>
-  </si>
-  <si>
     <t xml:space="preserve">BRD raised with CRPL, SOW finalized, FSD and efforts required, under development </t>
   </si>
   <si>
@@ -435,13 +429,22 @@
   </si>
   <si>
     <t>Scoping.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under Development </t>
+  </si>
+  <si>
+    <t xml:space="preserve">FSD Approved </t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBT Threading </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -463,6 +466,13 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -645,7 +655,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -707,6 +717,7 @@
     <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -999,8 +1010,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F61" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
-  <autoFilter ref="A1:F61"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F62" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
+  <autoFilter ref="A1:F62"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Allocation" dataDxfId="5"/>
     <tableColumn id="2" name="Category" dataDxfId="4"/>
@@ -1276,7 +1287,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
@@ -1324,7 +1335,7 @@
         <v>95</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1378,7 +1389,7 @@
         <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E5" s="36" t="s">
         <v>95</v>
@@ -1435,16 +1446,16 @@
         <v>27</v>
       </c>
       <c r="C8" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="F8" s="34" t="s">
         <v>134</v>
-      </c>
-      <c r="D8" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="E8" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="F8" s="34" t="s">
-        <v>136</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1691,21 +1702,17 @@
       <c r="A21" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="19" t="s">
+      <c r="B21" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" s="53" t="s">
         <v>8</v>
       </c>
       <c r="D21" s="44" t="s">
-        <v>121</v>
-      </c>
-      <c r="E21" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="F21" s="46" t="s">
-        <v>124</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="E21" s="47"/>
+      <c r="F21" s="46"/>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="43" t="s">
@@ -1715,56 +1722,56 @@
         <v>7</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D22" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="47">
-        <v>46176</v>
+        <v>121</v>
+      </c>
+      <c r="E22" s="45" t="s">
+        <v>95</v>
       </c>
       <c r="F22" s="46" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="B23" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D23" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="47">
+        <v>46176</v>
+      </c>
+      <c r="F23" s="46" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="B23" s="50" t="s">
+      <c r="B24" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C24" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="21" t="s">
+      <c r="D24" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="E23" s="45" t="s">
+      <c r="E24" s="45" t="s">
         <v>96</v>
       </c>
-      <c r="F23" s="22" t="s">
+      <c r="F24" s="22" t="s">
         <v>110</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>29</v>
-      </c>
-      <c r="E24" s="33">
-        <v>46241</v>
-      </c>
-      <c r="F24" s="34" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1778,13 +1785,13 @@
         <v>18</v>
       </c>
       <c r="D25" s="32" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E25" s="33">
-        <v>46261</v>
+        <v>46241</v>
       </c>
       <c r="F25" s="34" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1792,119 +1799,119 @@
         <v>26</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C26" s="31" t="s">
         <v>18</v>
       </c>
       <c r="D26" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="33">
+        <v>46261</v>
+      </c>
+      <c r="F26" s="34" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>18</v>
+      </c>
+      <c r="D27" s="32" t="s">
         <v>33</v>
       </c>
-      <c r="E26" s="33">
+      <c r="E27" s="33">
         <v>46227</v>
       </c>
-      <c r="F26" s="34" t="s">
+      <c r="F27" s="34" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E27" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="F27" s="18" t="s">
-        <v>69</v>
-      </c>
-    </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="15" t="s">
         <v>34</v>
       </c>
       <c r="B28" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>70</v>
+      <c r="C28" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>68</v>
       </c>
       <c r="E28" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="F28" s="9" t="s">
-        <v>89</v>
+      <c r="F28" s="18" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C30" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D30" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E30" s="3">
         <v>46125</v>
       </c>
-      <c r="F29" s="9" t="s">
+      <c r="F30" s="9" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="24" t="s">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="25" t="s">
+      <c r="B31" s="25" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="25" t="s">
+      <c r="C31" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D30" s="17" t="s">
+      <c r="D31" s="17" t="s">
         <v>90</v>
       </c>
-      <c r="E30" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="F30" s="18" t="s">
+      <c r="E31" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="F31" s="18" t="s">
         <v>91</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>119</v>
-      </c>
-      <c r="E31" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="F31" s="18" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1918,33 +1925,33 @@
         <v>44</v>
       </c>
       <c r="D32" s="17" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="E32" s="36" t="s">
         <v>95</v>
       </c>
       <c r="F32" s="18" t="s">
-        <v>74</v>
+        <v>101</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>35</v>
+      <c r="C33" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="D33" s="17" t="s">
+        <v>103</v>
       </c>
       <c r="E33" s="36" t="s">
         <v>95</v>
       </c>
-      <c r="F33" s="9" t="s">
-        <v>94</v>
+      <c r="F33" s="18" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1955,13 +1962,13 @@
         <v>27</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>18</v>
+        <v>81</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E34" s="36">
-        <v>46276</v>
+        <v>35</v>
+      </c>
+      <c r="E34" s="36" t="s">
+        <v>95</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>94</v>
@@ -1975,16 +1982,16 @@
         <v>27</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E35" s="36" t="s">
-        <v>95</v>
+        <v>36</v>
+      </c>
+      <c r="E35" s="36">
+        <v>46276</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>37</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1995,16 +2002,16 @@
         <v>27</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E36" s="3">
-        <v>46161</v>
+        <v>120</v>
+      </c>
+      <c r="E36" s="36" t="s">
+        <v>95</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2018,13 +2025,13 @@
         <v>18</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="E37" s="3">
-        <v>46147</v>
+        <v>46161</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2038,33 +2045,33 @@
         <v>18</v>
       </c>
       <c r="D38" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E38" s="3">
+        <v>46147</v>
+      </c>
+      <c r="F38" s="9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E38" s="3">
+      <c r="E39" s="3">
         <v>46122</v>
       </c>
-      <c r="F38" s="9" t="s">
+      <c r="F39" s="9" t="s">
         <v>43</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="B39" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="C39" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="D39" s="41" t="s">
-        <v>104</v>
-      </c>
-      <c r="E39" s="45" t="s">
-        <v>96</v>
-      </c>
-      <c r="F39" s="42" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2072,13 +2079,13 @@
         <v>34</v>
       </c>
       <c r="B40" s="40" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C40" s="40" t="s">
         <v>96</v>
       </c>
       <c r="D40" s="41" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E40" s="45" t="s">
         <v>96</v>
@@ -2088,23 +2095,23 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B41" s="4" t="s">
+      <c r="A41" s="39" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="C41" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E41" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="F41" s="10" t="s">
-        <v>77</v>
+      <c r="C41" s="40" t="s">
+        <v>96</v>
+      </c>
+      <c r="D41" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="E41" s="45" t="s">
+        <v>96</v>
+      </c>
+      <c r="F41" s="42" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2112,19 +2119,19 @@
         <v>65</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>14</v>
+        <v>81</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E42" s="36" t="s">
         <v>95</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2132,19 +2139,19 @@
         <v>65</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E43" s="6">
-        <v>46059</v>
+        <v>46</v>
+      </c>
+      <c r="E43" s="36" t="s">
+        <v>95</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2152,19 +2159,19 @@
         <v>65</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="C44" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E44" s="6">
-        <v>46181</v>
+        <v>46059</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2172,19 +2179,19 @@
         <v>65</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="C45" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>76</v>
+        <v>49</v>
       </c>
       <c r="E45" s="6">
-        <v>46227</v>
+        <v>46181</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2192,19 +2199,19 @@
         <v>65</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="E46" s="36" t="s">
-        <v>95</v>
+        <v>76</v>
+      </c>
+      <c r="E46" s="6">
+        <v>46227</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>128</v>
+        <v>51</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2212,19 +2219,19 @@
         <v>65</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E47" s="6">
-        <v>46161</v>
+        <v>115</v>
+      </c>
+      <c r="E47" s="36" t="s">
+        <v>95</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2235,16 +2242,16 @@
         <v>27</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E48" s="36" t="s">
-        <v>95</v>
+        <v>52</v>
+      </c>
+      <c r="E48" s="6">
+        <v>46161</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2255,10 +2262,10 @@
         <v>27</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E49" s="36" t="s">
         <v>95</v>
@@ -2275,16 +2282,16 @@
         <v>27</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E50" s="6">
-        <v>46181</v>
+        <v>117</v>
+      </c>
+      <c r="E50" s="36" t="s">
+        <v>95</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>80</v>
+        <v>136</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2295,16 +2302,16 @@
         <v>27</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>96</v>
+        <v>18</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E51" s="36" t="s">
-        <v>96</v>
+        <v>53</v>
+      </c>
+      <c r="E51" s="6">
+        <v>46181</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>110</v>
+        <v>80</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2312,13 +2319,13 @@
         <v>65</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>96</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E52" s="36" t="s">
         <v>96</v>
@@ -2332,13 +2339,13 @@
         <v>65</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C53" s="4" t="s">
         <v>96</v>
       </c>
       <c r="D53" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E53" s="36" t="s">
         <v>96</v>
@@ -2358,7 +2365,7 @@
         <v>96</v>
       </c>
       <c r="D54" s="5" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E54" s="36" t="s">
         <v>96</v>
@@ -2368,43 +2375,43 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="23" t="s">
+      <c r="A55" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E55" s="36" t="s">
+        <v>96</v>
+      </c>
+      <c r="F55" s="10" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="B55" s="20" t="s">
+      <c r="B56" s="20" t="s">
         <v>82</v>
       </c>
-      <c r="C55" s="20" t="s">
+      <c r="C56" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="D55" s="21" t="s">
+      <c r="D56" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="E55" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="F55" s="22" t="s">
+      <c r="E56" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="F56" s="22" t="s">
         <v>84</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B56" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="D56" s="35" t="s">
-        <v>63</v>
-      </c>
-      <c r="E56" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="F56" s="35" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2412,39 +2419,39 @@
         <v>61</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>106</v>
+        <v>62</v>
       </c>
       <c r="C57" s="19" t="s">
         <v>96</v>
       </c>
       <c r="D57" s="35" t="s">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="E57" s="51" t="s">
         <v>96</v>
       </c>
       <c r="F57" s="35" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B58" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="C58" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="D58" s="35" t="s">
+        <v>106</v>
+      </c>
+      <c r="E58" s="51" t="s">
+        <v>96</v>
+      </c>
+      <c r="F58" s="35" t="s">
         <v>110</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="B58" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="E58" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="F58" s="29" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2452,19 +2459,19 @@
         <v>57</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C59" s="27" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="28" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="E59" s="36" t="s">
         <v>95</v>
       </c>
       <c r="F59" s="29" t="s">
-        <v>32</v>
+        <v>122</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2472,19 +2479,19 @@
         <v>57</v>
       </c>
       <c r="B60" s="27" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C60" s="27" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="D60" s="28" t="s">
-        <v>75</v>
+        <v>31</v>
       </c>
       <c r="E60" s="36" t="s">
         <v>95</v>
       </c>
       <c r="F60" s="29" t="s">
-        <v>123</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2492,18 +2499,38 @@
         <v>57</v>
       </c>
       <c r="B61" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D61" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="E61" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="F61" s="29" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B62" s="27" t="s">
         <v>112</v>
       </c>
-      <c r="C61" s="27" t="s">
+      <c r="C62" s="27" t="s">
         <v>96</v>
       </c>
-      <c r="D61" s="28" t="s">
+      <c r="D62" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="E61" s="52" t="s">
+      <c r="E62" s="52" t="s">
         <v>96</v>
       </c>
-      <c r="F61" s="29" t="s">
+      <c r="F62" s="29" t="s">
         <v>110</v>
       </c>
     </row>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -248,9 +248,6 @@
     <t>Live.</t>
   </si>
   <si>
-    <t>BRD shared.</t>
-  </si>
-  <si>
     <t>Banker Cheque collection via CRPL</t>
   </si>
   <si>
@@ -335,9 +332,6 @@
     <t xml:space="preserve">Branch collection/ API Billers </t>
   </si>
   <si>
-    <t>ME Onboarding</t>
-  </si>
-  <si>
     <t>Payment Portal Front-Office</t>
   </si>
   <si>
@@ -362,9 +356,6 @@
     <t>Cash over the counter (COC)</t>
   </si>
   <si>
-    <t>Payments</t>
-  </si>
-  <si>
     <t>SWAPS</t>
   </si>
   <si>
@@ -438,6 +429,15 @@
   </si>
   <si>
     <t xml:space="preserve">IBT Threading </t>
+  </si>
+  <si>
+    <t>Sania Malik</t>
+  </si>
+  <si>
+    <t>Enhancment of FT Amount limit for IBT</t>
+  </si>
+  <si>
+    <t>BRD Shared.</t>
   </si>
 </sst>
 </file>
@@ -655,7 +655,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -718,6 +718,11 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1329,13 +1334,13 @@
         <v>44</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="E2" s="36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F2" s="10" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1349,10 +1354,10 @@
         <v>8</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E3" s="36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F3" s="10" t="s">
         <v>47</v>
@@ -1372,7 +1377,7 @@
         <v>11</v>
       </c>
       <c r="E4" s="45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F4" s="46" t="s">
         <v>66</v>
@@ -1389,13 +1394,13 @@
         <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E5" s="36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1412,7 +1417,7 @@
         <v>54</v>
       </c>
       <c r="E6" s="36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F6" s="9" t="s">
         <v>55</v>
@@ -1432,7 +1437,7 @@
         <v>58</v>
       </c>
       <c r="E7" s="52" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F7" s="29" t="s">
         <v>59</v>
@@ -1446,16 +1451,16 @@
         <v>27</v>
       </c>
       <c r="C8" s="31" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F8" s="34" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1472,7 +1477,7 @@
         <v>9</v>
       </c>
       <c r="E9" s="45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F9" s="46" t="s">
         <v>67</v>
@@ -1492,7 +1497,7 @@
         <v>10</v>
       </c>
       <c r="E10" s="45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F10" s="46" t="s">
         <v>66</v>
@@ -1512,7 +1517,7 @@
         <v>12</v>
       </c>
       <c r="E11" s="45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F11" s="46" t="s">
         <v>13</v>
@@ -1529,13 +1534,13 @@
         <v>18</v>
       </c>
       <c r="D12" s="44" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E12" s="45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F12" s="46" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1552,7 +1557,7 @@
         <v>15</v>
       </c>
       <c r="E13" s="45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F13" s="46" t="s">
         <v>16</v>
@@ -1572,10 +1577,10 @@
         <v>17</v>
       </c>
       <c r="E14" s="45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F14" s="46" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="15" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.25">
@@ -1603,19 +1608,19 @@
         <v>6</v>
       </c>
       <c r="B16" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="C16" s="50" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="50" t="s">
-        <v>81</v>
-      </c>
-      <c r="D16" s="21" t="s">
+      <c r="E16" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="F16" s="22" t="s">
         <v>86</v>
-      </c>
-      <c r="E16" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="F16" s="22" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1629,10 +1634,10 @@
         <v>18</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E17" s="45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F17" s="22" t="s">
         <v>73</v>
@@ -1669,10 +1674,10 @@
         <v>18</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E19" s="45" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F19" s="49" t="s">
         <v>73</v>
@@ -1709,7 +1714,7 @@
         <v>8</v>
       </c>
       <c r="D21" s="44" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E21" s="47"/>
       <c r="F21" s="46"/>
@@ -1725,13 +1730,13 @@
         <v>8</v>
       </c>
       <c r="D22" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="E22" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" s="46" t="s">
         <v>121</v>
-      </c>
-      <c r="E22" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="F22" s="46" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1751,27 +1756,27 @@
         <v>46176</v>
       </c>
       <c r="F23" s="46" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="43" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B24" s="50" t="s">
         <v>7</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D24" s="21" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E24" s="45" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F24" s="22" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1791,7 +1796,7 @@
         <v>46241</v>
       </c>
       <c r="F25" s="34" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1811,7 +1816,7 @@
         <v>46261</v>
       </c>
       <c r="F26" s="34" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1831,127 +1836,127 @@
         <v>46227</v>
       </c>
       <c r="F27" s="34" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="7" t="s">
         <v>34</v>
       </c>
       <c r="B28" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C28" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>68</v>
+      <c r="C28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>70</v>
       </c>
       <c r="E28" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="F28" s="18" t="s">
-        <v>69</v>
+        <v>94</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="16" t="s">
-        <v>7</v>
+      <c r="B29" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E29" s="3">
+        <v>46125</v>
+      </c>
+      <c r="F29" s="9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D30" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E30" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="F30" s="18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E29" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E30" s="3">
-        <v>46125</v>
-      </c>
-      <c r="F30" s="9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31" s="25" t="s">
-        <v>8</v>
-      </c>
       <c r="D31" s="17" t="s">
-        <v>90</v>
+        <v>116</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F31" s="18" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="D32" s="17" t="s">
-        <v>119</v>
+      <c r="C32" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="F32" s="18" t="s">
-        <v>101</v>
+        <v>94</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C33" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="D33" s="17" t="s">
-        <v>103</v>
-      </c>
-      <c r="E33" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="F33" s="18" t="s">
-        <v>74</v>
+      <c r="C33" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E33" s="36">
+        <v>46276</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1962,16 +1967,16 @@
         <v>27</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>81</v>
+        <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="E34" s="36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>94</v>
+        <v>37</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1985,13 +1990,13 @@
         <v>18</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E35" s="36">
-        <v>46276</v>
+        <v>71</v>
+      </c>
+      <c r="E35" s="3">
+        <v>46161</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>94</v>
+        <v>39</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2002,16 +2007,16 @@
         <v>27</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E36" s="36" t="s">
-        <v>95</v>
+        <v>40</v>
+      </c>
+      <c r="E36" s="3">
+        <v>46147</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
@@ -2025,93 +2030,93 @@
         <v>18</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>71</v>
+        <v>42</v>
       </c>
       <c r="E37" s="3">
-        <v>46161</v>
+        <v>46122</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E38" s="3">
-        <v>46147</v>
-      </c>
-      <c r="F38" s="9" t="s">
-        <v>41</v>
+      <c r="C38" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="D38" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="E38" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="F38" s="42" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="7" t="s">
+      <c r="A39" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="40" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="D39" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="E39" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="F39" s="42" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E40" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B41" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C39" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E39" s="3">
-        <v>46122</v>
-      </c>
-      <c r="F39" s="9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="B40" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="C40" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="D40" s="41" t="s">
-        <v>104</v>
-      </c>
-      <c r="E40" s="45" t="s">
-        <v>96</v>
-      </c>
-      <c r="F40" s="42" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="B41" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="40" t="s">
-        <v>96</v>
-      </c>
-      <c r="D41" s="41" t="s">
-        <v>105</v>
-      </c>
-      <c r="E41" s="45" t="s">
-        <v>96</v>
-      </c>
-      <c r="F41" s="42" t="s">
-        <v>110</v>
+      <c r="C41" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="E41" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2122,16 +2127,16 @@
         <v>7</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>81</v>
+        <v>18</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="E42" s="36" t="s">
-        <v>95</v>
+        <v>48</v>
+      </c>
+      <c r="E42" s="6">
+        <v>46059</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2139,19 +2144,19 @@
         <v>65</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E43" s="36" t="s">
-        <v>95</v>
+        <v>49</v>
+      </c>
+      <c r="E43" s="6">
+        <v>46181</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2165,13 +2170,13 @@
         <v>18</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="E44" s="6">
-        <v>46059</v>
+        <v>46227</v>
       </c>
       <c r="F44" s="10" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2182,36 +2187,36 @@
         <v>38</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="E45" s="6">
-        <v>46181</v>
+        <v>112</v>
+      </c>
+      <c r="E45" s="36" t="s">
+        <v>94</v>
       </c>
       <c r="F45" s="10" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
         <v>65</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C46" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="E46" s="6">
-        <v>46227</v>
+        <v>46161</v>
       </c>
       <c r="F46" s="10" t="s">
-        <v>51</v>
+        <v>126</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2219,19 +2224,19 @@
         <v>65</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C47" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="E47" s="36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F47" s="10" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -2242,19 +2247,19 @@
         <v>27</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E48" s="6">
-        <v>46161</v>
+        <v>114</v>
+      </c>
+      <c r="E48" s="36" t="s">
+        <v>94</v>
       </c>
       <c r="F48" s="10" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
         <v>65</v>
       </c>
@@ -2262,19 +2267,19 @@
         <v>27</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="E49" s="36" t="s">
-        <v>95</v>
+        <v>53</v>
+      </c>
+      <c r="E49" s="6">
+        <v>46181</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="8" t="s">
         <v>65</v>
       </c>
@@ -2282,36 +2287,36 @@
         <v>27</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="E50" s="36" t="s">
         <v>95</v>
       </c>
       <c r="F50" s="10" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="8" t="s">
         <v>65</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E51" s="6">
-        <v>46181</v>
+        <v>106</v>
+      </c>
+      <c r="E51" s="36" t="s">
+        <v>95</v>
       </c>
       <c r="F51" s="10" t="s">
-        <v>80</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2322,16 +2327,16 @@
         <v>27</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D52" s="5" t="s">
         <v>107</v>
       </c>
       <c r="E52" s="36" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F52" s="10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -2339,79 +2344,79 @@
         <v>65</v>
       </c>
       <c r="B53" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="E53" s="36" t="s">
+        <v>95</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C53" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="E53" s="36" t="s">
-        <v>96</v>
-      </c>
-      <c r="F53" s="10" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D54" s="5" t="s">
-        <v>109</v>
+      <c r="C54" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" s="17" t="s">
+        <v>68</v>
       </c>
       <c r="E54" s="36" t="s">
-        <v>96</v>
-      </c>
-      <c r="F54" s="10" t="s">
-        <v>110</v>
+        <v>94</v>
+      </c>
+      <c r="F54" s="18" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D55" s="5" t="s">
-        <v>111</v>
+      <c r="A55" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="C55" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D55" s="21" t="s">
+        <v>82</v>
       </c>
       <c r="E55" s="36" t="s">
-        <v>96</v>
-      </c>
-      <c r="F55" s="10" t="s">
-        <v>110</v>
+        <v>94</v>
+      </c>
+      <c r="F55" s="22" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="23" t="s">
+      <c r="A56" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="B56" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="C56" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="D56" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="E56" s="36" t="s">
+      <c r="B56" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="C56" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="F56" s="22" t="s">
-        <v>84</v>
+      <c r="D56" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="E56" s="51" t="s">
+        <v>95</v>
+      </c>
+      <c r="F56" s="35" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -2419,39 +2424,39 @@
         <v>61</v>
       </c>
       <c r="B57" s="19" t="s">
-        <v>62</v>
+        <v>104</v>
       </c>
       <c r="C57" s="19" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D57" s="35" t="s">
-        <v>63</v>
+        <v>104</v>
       </c>
       <c r="E57" s="51" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F57" s="35" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B58" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="C58" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="D58" s="35" t="s">
-        <v>106</v>
-      </c>
-      <c r="E58" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="F58" s="35" t="s">
-        <v>110</v>
+      <c r="A58" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="E58" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="F58" s="29" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2459,19 +2464,19 @@
         <v>57</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C59" s="27" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="28" t="s">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="E59" s="36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F59" s="29" t="s">
-        <v>122</v>
+        <v>32</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2479,19 +2484,19 @@
         <v>57</v>
       </c>
       <c r="B60" s="27" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C60" s="27" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="D60" s="28" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="E60" s="36" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F60" s="29" t="s">
-        <v>32</v>
+        <v>120</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2499,39 +2504,39 @@
         <v>57</v>
       </c>
       <c r="B61" s="27" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C61" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="D61" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="E61" s="52" t="s">
+        <v>95</v>
+      </c>
+      <c r="F61" s="29" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="54" t="s">
+        <v>135</v>
+      </c>
+      <c r="B62" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="C62" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="D61" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="E61" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="F61" s="29" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="B62" s="27" t="s">
-        <v>112</v>
-      </c>
-      <c r="C62" s="27" t="s">
-        <v>96</v>
-      </c>
-      <c r="D62" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="E62" s="52" t="s">
-        <v>96</v>
-      </c>
-      <c r="F62" s="29" t="s">
-        <v>110</v>
+      <c r="D62" s="41" t="s">
+        <v>136</v>
+      </c>
+      <c r="E62" s="56" t="s">
+        <v>94</v>
+      </c>
+      <c r="F62" s="42" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="141">
   <si>
     <t>Allocation</t>
   </si>
@@ -438,6 +438,15 @@
   </si>
   <si>
     <t>BRD Shared.</t>
+  </si>
+  <si>
+    <t>Punjab Health commission</t>
+  </si>
+  <si>
+    <t>API Shared</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UBCS API Response </t>
   </si>
 </sst>
 </file>
@@ -655,7 +664,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -723,6 +732,7 @@
     <xf numFmtId="14" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1015,8 +1025,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F62" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
-  <autoFilter ref="A1:F62"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F64" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
+  <autoFilter ref="A1:F64"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Allocation" dataDxfId="5"/>
     <tableColumn id="2" name="Category" dataDxfId="4"/>
@@ -1292,7 +1302,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
@@ -1707,17 +1717,21 @@
       <c r="A21" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="C21" s="53" t="s">
+      <c r="B21" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="19" t="s">
         <v>8</v>
       </c>
       <c r="D21" s="44" t="s">
-        <v>134</v>
-      </c>
-      <c r="E21" s="47"/>
-      <c r="F21" s="46"/>
+        <v>118</v>
+      </c>
+      <c r="E21" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="F21" s="46" t="s">
+        <v>121</v>
+      </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="43" t="s">
@@ -1727,56 +1741,56 @@
         <v>7</v>
       </c>
       <c r="C22" s="19" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D22" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="E22" s="45" t="s">
-        <v>94</v>
+        <v>25</v>
+      </c>
+      <c r="E22" s="47">
+        <v>46176</v>
       </c>
       <c r="F22" s="46" t="s">
-        <v>121</v>
+        <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="43" t="s">
-        <v>6</v>
-      </c>
-      <c r="B23" s="19" t="s">
+        <v>115</v>
+      </c>
+      <c r="B23" s="50" t="s">
         <v>7</v>
       </c>
       <c r="C23" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" s="21" t="s">
+        <v>101</v>
+      </c>
+      <c r="E23" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="30" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="44" t="s">
-        <v>25</v>
-      </c>
-      <c r="E23" s="47">
-        <v>46176</v>
-      </c>
-      <c r="F23" s="46" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="43" t="s">
-        <v>115</v>
-      </c>
-      <c r="B24" s="50" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D24" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="E24" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="F24" s="22" t="s">
-        <v>108</v>
+      <c r="D24" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="33">
+        <v>46241</v>
+      </c>
+      <c r="F24" s="34" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1790,13 +1804,13 @@
         <v>18</v>
       </c>
       <c r="D25" s="32" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E25" s="33">
-        <v>46241</v>
+        <v>46261</v>
       </c>
       <c r="F25" s="34" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1804,119 +1818,119 @@
         <v>26</v>
       </c>
       <c r="B26" s="31" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C26" s="31" t="s">
         <v>18</v>
       </c>
       <c r="D26" s="32" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="E26" s="33">
-        <v>46261</v>
+        <v>46227</v>
       </c>
       <c r="F26" s="34" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="D27" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="E27" s="33">
-        <v>46227</v>
-      </c>
-      <c r="F27" s="34" t="s">
-        <v>123</v>
+      <c r="A27" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E27" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="16" t="s">
-        <v>7</v>
+      <c r="B28" s="1" t="s">
+        <v>27</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E28" s="3">
+        <v>46125</v>
+      </c>
+      <c r="F28" s="9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E29" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E28" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E29" s="3">
-        <v>46125</v>
-      </c>
-      <c r="F29" s="9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" s="25" t="s">
-        <v>8</v>
-      </c>
       <c r="D30" s="17" t="s">
-        <v>89</v>
+        <v>116</v>
       </c>
       <c r="E30" s="36" t="s">
         <v>94</v>
       </c>
       <c r="F30" s="18" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C31" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>116</v>
+      <c r="C31" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>35</v>
       </c>
       <c r="E31" s="36" t="s">
         <v>94</v>
       </c>
-      <c r="F31" s="18" t="s">
-        <v>100</v>
+      <c r="F31" s="9" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1927,13 +1941,13 @@
         <v>27</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E32" s="36" t="s">
-        <v>94</v>
+        <v>36</v>
+      </c>
+      <c r="E32" s="36">
+        <v>46276</v>
       </c>
       <c r="F32" s="9" t="s">
         <v>93</v>
@@ -1947,16 +1961,16 @@
         <v>27</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E33" s="36">
-        <v>46276</v>
+        <v>117</v>
+      </c>
+      <c r="E33" s="36" t="s">
+        <v>94</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>93</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1967,16 +1981,16 @@
         <v>27</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E34" s="36" t="s">
-        <v>94</v>
+        <v>71</v>
+      </c>
+      <c r="E34" s="3">
+        <v>46161</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -1990,13 +2004,13 @@
         <v>18</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="E35" s="3">
-        <v>46161</v>
+        <v>46147</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -2010,33 +2024,33 @@
         <v>18</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E36" s="3">
-        <v>46147</v>
+        <v>46122</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="7" t="s">
+      <c r="A37" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E37" s="3">
-        <v>46122</v>
-      </c>
-      <c r="F37" s="9" t="s">
-        <v>43</v>
+      <c r="C37" s="40" t="s">
+        <v>95</v>
+      </c>
+      <c r="D37" s="41" t="s">
+        <v>102</v>
+      </c>
+      <c r="E37" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="F37" s="42" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
@@ -2044,13 +2058,13 @@
         <v>34</v>
       </c>
       <c r="B38" s="40" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C38" s="40" t="s">
         <v>95</v>
       </c>
       <c r="D38" s="41" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E38" s="45" t="s">
         <v>95</v>
@@ -2060,23 +2074,23 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="39" t="s">
-        <v>34</v>
-      </c>
-      <c r="B39" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="40" t="s">
-        <v>95</v>
-      </c>
-      <c r="D39" s="41" t="s">
-        <v>103</v>
-      </c>
-      <c r="E39" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="F39" s="42" t="s">
-        <v>108</v>
+      <c r="A39" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="E39" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2084,19 +2098,19 @@
         <v>65</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>80</v>
+        <v>14</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E40" s="36" t="s">
         <v>94</v>
       </c>
       <c r="F40" s="10" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2104,19 +2118,19 @@
         <v>65</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="E41" s="36" t="s">
-        <v>94</v>
+        <v>48</v>
+      </c>
+      <c r="E41" s="6">
+        <v>46059</v>
       </c>
       <c r="F41" s="10" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2124,19 +2138,19 @@
         <v>65</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="C42" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E42" s="6">
-        <v>46059</v>
+        <v>46181</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2144,42 +2158,40 @@
         <v>65</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="C43" s="4" t="s">
         <v>18</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="E43" s="6">
-        <v>46181</v>
+        <v>46227</v>
       </c>
       <c r="F43" s="10" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="8" t="s">
+      <c r="A44" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="B44" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E44" s="6">
-        <v>46227</v>
-      </c>
-      <c r="F44" s="10" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B44" s="55" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="55" t="s">
+        <v>8</v>
+      </c>
+      <c r="D44" s="41" t="s">
+        <v>140</v>
+      </c>
+      <c r="E44" s="57" t="s">
+        <v>94</v>
+      </c>
+      <c r="F44" s="42"/>
+    </row>
+    <row r="45" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="8" t="s">
         <v>65</v>
       </c>
@@ -2199,7 +2211,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
         <v>65</v>
       </c>
@@ -2219,7 +2231,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="8" t="s">
         <v>65</v>
       </c>
@@ -2259,7 +2271,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="49" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="8" t="s">
         <v>65</v>
       </c>
@@ -2440,23 +2452,23 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="26" t="s">
+      <c r="A58" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="B58" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="27" t="s">
+      <c r="B58" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="C58" s="53" t="s">
         <v>8</v>
       </c>
-      <c r="D58" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="E58" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="F58" s="29" t="s">
-        <v>119</v>
+      <c r="D58" s="44" t="s">
+        <v>134</v>
+      </c>
+      <c r="E58" s="47" t="s">
+        <v>94</v>
+      </c>
+      <c r="F58" s="46" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -2464,19 +2476,19 @@
         <v>57</v>
       </c>
       <c r="B59" s="27" t="s">
-        <v>28</v>
+        <v>7</v>
       </c>
       <c r="C59" s="27" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="28" t="s">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="E59" s="36" t="s">
         <v>94</v>
       </c>
       <c r="F59" s="29" t="s">
-        <v>32</v>
+        <v>119</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -2484,19 +2496,19 @@
         <v>57</v>
       </c>
       <c r="B60" s="27" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C60" s="27" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="D60" s="28" t="s">
-        <v>74</v>
+        <v>31</v>
       </c>
       <c r="E60" s="36" t="s">
         <v>94</v>
       </c>
       <c r="F60" s="29" t="s">
-        <v>120</v>
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2504,39 +2516,79 @@
         <v>57</v>
       </c>
       <c r="B61" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="D61" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="E61" s="36" t="s">
+        <v>94</v>
+      </c>
+      <c r="F61" s="29" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="B62" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C61" s="27" t="s">
+      <c r="C62" s="27" t="s">
         <v>95</v>
       </c>
-      <c r="D61" s="28" t="s">
+      <c r="D62" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="E61" s="52" t="s">
+      <c r="E62" s="52" t="s">
         <v>95</v>
       </c>
-      <c r="F61" s="29" t="s">
+      <c r="F62" s="29" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="54" t="s">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="54" t="s">
         <v>135</v>
       </c>
-      <c r="B62" s="55" t="s">
+      <c r="B63" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="C62" s="55" t="s">
+      <c r="C63" s="55" t="s">
         <v>44</v>
       </c>
-      <c r="D62" s="41" t="s">
+      <c r="D63" s="41" t="s">
         <v>136</v>
       </c>
-      <c r="E62" s="56" t="s">
-        <v>94</v>
-      </c>
-      <c r="F62" s="42" t="s">
+      <c r="E63" s="56" t="s">
+        <v>94</v>
+      </c>
+      <c r="F63" s="42" t="s">
         <v>137</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="54" t="s">
+        <v>135</v>
+      </c>
+      <c r="B64" s="55" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="D64" s="41" t="s">
+        <v>138</v>
+      </c>
+      <c r="E64" s="56" t="s">
+        <v>94</v>
+      </c>
+      <c r="F64" s="42" t="s">
+        <v>139</v>
       </c>
     </row>
   </sheetData>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="142">
   <si>
     <t>Allocation</t>
   </si>
@@ -447,6 +447,9 @@
   </si>
   <si>
     <t xml:space="preserve">UBCS API Response </t>
+  </si>
+  <si>
+    <t>will go live on this Friday</t>
   </si>
 </sst>
 </file>
@@ -664,21 +667,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -698,13 +698,11 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -716,7 +714,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -732,38 +729,26 @@
     <xf numFmtId="14" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="10">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
-      </border>
-    </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
       <fill>
@@ -772,6 +757,7 @@
           <bgColor theme="5" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
@@ -794,7 +780,27 @@
           <bgColor theme="5" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
@@ -807,12 +813,6 @@
         <bottom style="thin">
           <color auto="1"/>
         </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
       </border>
     </dxf>
     <dxf>
@@ -1032,8 +1032,8 @@
     <tableColumn id="2" name="Category" dataDxfId="4"/>
     <tableColumn id="3" name="Status " dataDxfId="3"/>
     <tableColumn id="4" name="Mandate" dataDxfId="2"/>
-    <tableColumn id="5" name="Live Date" dataDxfId="1"/>
-    <tableColumn id="6" name="Update" dataDxfId="0"/>
+    <tableColumn id="5" name="Live Date" dataDxfId="0"/>
+    <tableColumn id="6" name="Update" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1309,92 +1309,92 @@
     <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="51.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="37" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" style="55" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="192.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="F1" s="11" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="B2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="E2" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="F2" s="10" t="s">
+      <c r="E2" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E3" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="F3" s="10" t="s">
+      <c r="E3" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="8" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="43" t="s">
+      <c r="A4" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="19" t="s">
+      <c r="B4" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="44" t="s">
+      <c r="D4" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="F4" s="46" t="s">
+      <c r="E4" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4" s="41" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1406,15 +1406,15 @@
       <c r="D5" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E5" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="F5" s="9" t="s">
+      <c r="E5" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -1426,418 +1426,418 @@
       <c r="D6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="F6" s="9" t="s">
+      <c r="E6" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F6" s="7" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="26" t="s">
+      <c r="A7" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="52" t="s">
-        <v>94</v>
-      </c>
-      <c r="F7" s="29" t="s">
+      <c r="E7" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="F7" s="26" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="D8" s="32" t="s">
+      <c r="D8" s="29" t="s">
         <v>130</v>
       </c>
-      <c r="E8" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="F8" s="34" t="s">
+      <c r="E8" s="52" t="s">
+        <v>94</v>
+      </c>
+      <c r="F8" s="30" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="43" t="s">
+      <c r="A9" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="19" t="s">
+      <c r="B9" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="44" t="s">
+      <c r="D9" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="F9" s="46" t="s">
+      <c r="E9" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" s="41" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="43" t="s">
+      <c r="A10" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="19" t="s">
+      <c r="B10" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="44" t="s">
+      <c r="D10" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="F10" s="46" t="s">
+      <c r="E10" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="F10" s="41" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="43" t="s">
+      <c r="A11" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="19" t="s">
+      <c r="B11" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="44" t="s">
+      <c r="D11" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="F11" s="46" t="s">
+      <c r="E11" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="F11" s="41" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="43" t="s">
+      <c r="A12" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="19" t="s">
+      <c r="B12" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="44" t="s">
+      <c r="D12" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="E12" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="F12" s="46" t="s">
+      <c r="E12" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="F12" s="41" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="43" t="s">
+      <c r="A13" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="19" t="s">
+      <c r="B13" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="44" t="s">
+      <c r="D13" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="F13" s="46" t="s">
+      <c r="E13" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="F13" s="41" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="43" t="s">
+      <c r="A14" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="19" t="s">
+      <c r="B14" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="44" t="s">
+      <c r="D14" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" s="46" t="s">
+      <c r="E14" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="F14" s="41" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="38" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="43" t="s">
+    <row r="15" spans="1:6" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="19" t="s">
+      <c r="B15" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="44" t="s">
+      <c r="D15" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="47">
+      <c r="E15" s="40">
         <v>46218</v>
       </c>
-      <c r="F15" s="46" t="s">
+      <c r="F15" s="41" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="48" t="s">
+      <c r="A16" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="17" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="50" t="s">
+      <c r="C16" s="44" t="s">
         <v>80</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="18" t="s">
         <v>85</v>
       </c>
-      <c r="E16" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="F16" s="22" t="s">
+      <c r="E16" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="F16" s="19" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="48" t="s">
+      <c r="A17" s="42" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="20" t="s">
+      <c r="B17" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="21" t="s">
+      <c r="D17" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="E17" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="F17" s="22" t="s">
+      <c r="E17" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="F17" s="19" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="43" t="s">
+      <c r="A18" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="19" t="s">
+      <c r="B18" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="44" t="s">
+      <c r="D18" s="39" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="47">
+      <c r="E18" s="40">
         <v>46218</v>
       </c>
-      <c r="F18" s="46" t="s">
+      <c r="F18" s="41" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="20" t="s">
+      <c r="B19" s="17" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="21" t="s">
+      <c r="D19" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="E19" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="F19" s="49" t="s">
+      <c r="E19" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="43" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="43" t="s">
+      <c r="A20" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="19" t="s">
+      <c r="B20" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="44" t="s">
+      <c r="D20" s="39" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="47">
+      <c r="E20" s="40">
         <v>46220</v>
       </c>
-      <c r="F20" s="46" t="s">
+      <c r="F20" s="41" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="43" t="s">
+      <c r="A21" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="19" t="s">
+      <c r="B21" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="44" t="s">
+      <c r="D21" s="39" t="s">
         <v>118</v>
       </c>
-      <c r="E21" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="F21" s="46" t="s">
+      <c r="E21" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="F21" s="41" t="s">
         <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="43" t="s">
+      <c r="A22" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="19" t="s">
+      <c r="B22" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="44" t="s">
+      <c r="D22" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="E22" s="47">
+      <c r="E22" s="40">
         <v>46176</v>
       </c>
-      <c r="F22" s="46" t="s">
+      <c r="F22" s="41" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="43" t="s">
+      <c r="A23" s="38" t="s">
         <v>115</v>
       </c>
-      <c r="B23" s="50" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="19" t="s">
+      <c r="B23" s="44" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="D23" s="21" t="s">
+      <c r="D23" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="E23" s="45" t="s">
+      <c r="E23" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="F23" s="22" t="s">
+      <c r="F23" s="19" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="30" t="s">
+      <c r="A24" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="31" t="s">
+      <c r="B24" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="32" t="s">
+      <c r="D24" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="E24" s="33">
+      <c r="E24" s="52">
         <v>46241</v>
       </c>
-      <c r="F24" s="34" t="s">
+      <c r="F24" s="30" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="31" t="s">
+      <c r="C25" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="D25" s="32" t="s">
+      <c r="D25" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="E25" s="33">
+      <c r="E25" s="52">
         <v>46261</v>
       </c>
-      <c r="F25" s="34" t="s">
+      <c r="F25" s="30" t="s">
         <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="27" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="31" t="s">
+      <c r="B26" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="31" t="s">
+      <c r="C26" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="32" t="s">
+      <c r="D26" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="E26" s="33">
+      <c r="E26" s="52">
         <v>46227</v>
       </c>
-      <c r="F26" s="34" t="s">
+      <c r="F26" s="30" t="s">
         <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="13" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -1846,15 +1846,15 @@
       <c r="D27" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="F27" s="9" t="s">
+      <c r="E27" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" s="7" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
+      <c r="A28" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
@@ -1866,55 +1866,55 @@
       <c r="D28" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E28" s="3">
+      <c r="E28" s="53">
         <v>46125</v>
       </c>
-      <c r="F28" s="9" t="s">
+      <c r="F28" s="7" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="24" t="s">
+      <c r="A29" s="21" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="25" t="s">
+      <c r="B29" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="25" t="s">
+      <c r="C29" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="17" t="s">
+      <c r="D29" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="E29" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="F29" s="18" t="s">
+      <c r="E29" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="15" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="7" t="s">
+      <c r="A30" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D30" s="17" t="s">
+      <c r="D30" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="E30" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="F30" s="18" t="s">
+      <c r="E30" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F30" s="15" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -1926,15 +1926,15 @@
       <c r="D31" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E31" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="F31" s="9" t="s">
+      <c r="E31" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F31" s="7" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -1946,35 +1946,35 @@
       <c r="D32" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E32" s="36">
+      <c r="E32" s="32">
         <v>46276</v>
       </c>
-      <c r="F32" s="9" t="s">
+      <c r="F32" s="7" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>27</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="E33" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="F33" s="9" t="s">
+      <c r="E33" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F33" s="7" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -1986,15 +1986,15 @@
       <c r="D34" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E34" s="3">
+      <c r="E34" s="53">
         <v>46161</v>
       </c>
-      <c r="F34" s="9" t="s">
+      <c r="F34" s="7" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -2006,15 +2006,15 @@
       <c r="D35" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E35" s="3">
+      <c r="E35" s="53">
         <v>46147</v>
       </c>
-      <c r="F35" s="9" t="s">
+      <c r="F35" s="7" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="5" t="s">
         <v>34</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -2026,568 +2026,570 @@
       <c r="D36" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E36" s="3">
+      <c r="E36" s="53">
         <v>46122</v>
       </c>
-      <c r="F36" s="9" t="s">
+      <c r="F36" s="7" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="39" t="s">
+      <c r="A37" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="40" t="s">
+      <c r="B37" s="35" t="s">
         <v>27</v>
       </c>
-      <c r="C37" s="40" t="s">
+      <c r="C37" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="D37" s="41" t="s">
+      <c r="D37" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="E37" s="45" t="s">
+      <c r="E37" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="F37" s="42" t="s">
+      <c r="F37" s="37" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="39" t="s">
+      <c r="A38" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="B38" s="40" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="40" t="s">
+      <c r="B38" s="35" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="D38" s="41" t="s">
+      <c r="D38" s="36" t="s">
         <v>103</v>
       </c>
-      <c r="E38" s="45" t="s">
+      <c r="E38" s="40" t="s">
         <v>95</v>
       </c>
-      <c r="F38" s="42" t="s">
+      <c r="F38" s="37" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B39" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="4" t="s">
+      <c r="B39" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="5" t="s">
+      <c r="D39" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E39" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="F39" s="10" t="s">
+      <c r="E39" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F39" s="8" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="C40" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="E40" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="F40" s="10" t="s">
+      <c r="E40" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F40" s="8" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B41" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="4" t="s">
+      <c r="B41" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D41" s="5" t="s">
+      <c r="D41" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="E41" s="6">
+      <c r="E41" s="54">
         <v>46059</v>
       </c>
-      <c r="F41" s="10" t="s">
+      <c r="F41" s="8" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="C42" s="4" t="s">
+      <c r="C42" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="E42" s="6">
+      <c r="E42" s="54">
         <v>46181</v>
       </c>
-      <c r="F42" s="10" t="s">
+      <c r="F42" s="8" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B43" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="4" t="s">
+      <c r="B43" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D43" s="5" t="s">
+      <c r="D43" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="E43" s="6">
+      <c r="E43" s="54">
         <v>46227</v>
       </c>
-      <c r="F43" s="10" t="s">
+      <c r="F43" s="8" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="54" t="s">
+      <c r="A44" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="B44" s="55" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="55" t="s">
+      <c r="B44" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="49" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="E44" s="54">
+        <v>46311</v>
+      </c>
+      <c r="F44" s="37" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D44" s="41" t="s">
-        <v>140</v>
-      </c>
-      <c r="E44" s="57" t="s">
-        <v>94</v>
-      </c>
-      <c r="F44" s="42"/>
-    </row>
-    <row r="45" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="8" t="s">
+      <c r="D45" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="E45" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F45" s="8" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B45" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C45" s="4" t="s">
+      <c r="B46" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E46" s="54">
+        <v>46161</v>
+      </c>
+      <c r="F46" s="8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D45" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E45" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="F45" s="10" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="8" t="s">
+      <c r="D47" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="E47" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F47" s="8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B48" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C48" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E48" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F48" s="8" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C49" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D46" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="E46" s="6">
-        <v>46161</v>
-      </c>
-      <c r="F46" s="10" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="8" t="s">
+      <c r="D49" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E49" s="54">
+        <v>46181</v>
+      </c>
+      <c r="F49" s="8" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B50" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C47" s="4" t="s">
+      <c r="C50" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="E50" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E51" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="F51" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="E52" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="F52" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E53" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="F53" s="8" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="13" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="E54" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F54" s="15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="C55" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="D55" s="18" t="s">
+        <v>82</v>
+      </c>
+      <c r="E55" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F55" s="19" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>62</v>
+      </c>
+      <c r="C56" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D56" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="E56" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="F56" s="31" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="C57" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D57" s="31" t="s">
+        <v>104</v>
+      </c>
+      <c r="E57" s="45" t="s">
+        <v>95</v>
+      </c>
+      <c r="F57" s="31" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="38" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" s="47" t="s">
+        <v>27</v>
+      </c>
+      <c r="C58" s="47" t="s">
         <v>8</v>
       </c>
-      <c r="D47" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E47" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="F47" s="10" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B48" s="4" t="s">
+      <c r="D58" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="E58" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="F58" s="41" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B59" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="E59" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F59" s="26" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B60" s="24" t="s">
+        <v>28</v>
+      </c>
+      <c r="C60" s="24" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="25" t="s">
+        <v>31</v>
+      </c>
+      <c r="E60" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F60" s="26" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B61" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D61" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="E61" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="F61" s="26" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B62" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="C48" s="4" t="s">
+      <c r="C62" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="D62" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="E62" s="46" t="s">
+        <v>95</v>
+      </c>
+      <c r="F62" s="26" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="48" t="s">
+        <v>135</v>
+      </c>
+      <c r="B63" s="49" t="s">
+        <v>27</v>
+      </c>
+      <c r="C63" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="D48" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="E48" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="F48" s="10" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D49" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E49" s="6">
-        <v>46181</v>
-      </c>
-      <c r="F49" s="10" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D50" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="E50" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="F50" s="10" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D51" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="E51" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="F51" s="10" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D52" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E52" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="F52" s="10" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="E53" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="F53" s="10" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="D54" s="17" t="s">
-        <v>68</v>
-      </c>
-      <c r="E54" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="F54" s="18" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="B55" s="20" t="s">
-        <v>81</v>
-      </c>
-      <c r="C55" s="20" t="s">
+      <c r="D63" s="36" t="s">
+        <v>136</v>
+      </c>
+      <c r="E63" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="F63" s="37" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="48" t="s">
+        <v>135</v>
+      </c>
+      <c r="B64" s="49" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="49" t="s">
         <v>44</v>
       </c>
-      <c r="D55" s="21" t="s">
-        <v>82</v>
-      </c>
-      <c r="E55" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="F55" s="22" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B56" s="19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C56" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D56" s="35" t="s">
-        <v>63</v>
-      </c>
-      <c r="E56" s="51" t="s">
-        <v>95</v>
-      </c>
-      <c r="F56" s="35" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="B57" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="C57" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="D57" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="E57" s="51" t="s">
-        <v>95</v>
-      </c>
-      <c r="F57" s="35" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="B58" s="53" t="s">
-        <v>27</v>
-      </c>
-      <c r="C58" s="53" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="44" t="s">
-        <v>134</v>
-      </c>
-      <c r="E58" s="47" t="s">
-        <v>94</v>
-      </c>
-      <c r="F58" s="46" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="B59" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="E59" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="F59" s="29" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="B60" s="27" t="s">
-        <v>28</v>
-      </c>
-      <c r="C60" s="27" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="28" t="s">
-        <v>31</v>
-      </c>
-      <c r="E60" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="F60" s="29" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="B61" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="27" t="s">
-        <v>44</v>
-      </c>
-      <c r="D61" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="E61" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="F61" s="29" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="26" t="s">
-        <v>57</v>
-      </c>
-      <c r="B62" s="27" t="s">
-        <v>27</v>
-      </c>
-      <c r="C62" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="D62" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="E62" s="52" t="s">
-        <v>95</v>
-      </c>
-      <c r="F62" s="29" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="54" t="s">
-        <v>135</v>
-      </c>
-      <c r="B63" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="C63" s="55" t="s">
-        <v>44</v>
-      </c>
-      <c r="D63" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="E63" s="56" t="s">
-        <v>94</v>
-      </c>
-      <c r="F63" s="42" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="54" t="s">
-        <v>135</v>
-      </c>
-      <c r="B64" s="55" t="s">
-        <v>7</v>
-      </c>
-      <c r="C64" s="55" t="s">
-        <v>44</v>
-      </c>
-      <c r="D64" s="41" t="s">
+      <c r="D64" s="36" t="s">
         <v>138</v>
       </c>
-      <c r="E64" s="56" t="s">
-        <v>94</v>
-      </c>
-      <c r="F64" s="42" t="s">
+      <c r="E64" s="50" t="s">
+        <v>94</v>
+      </c>
+      <c r="F64" s="37" t="s">
         <v>139</v>
       </c>
     </row>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -449,7 +449,7 @@
     <t xml:space="preserve">UBCS API Response </t>
   </si>
   <si>
-    <t>will go live on this Friday</t>
+    <t>Transactions with higher amounts will be processed first, while multithreading will enable faster transaction processing.</t>
   </si>
 </sst>
 </file>
@@ -750,6 +750,26 @@
   </cellStyles>
   <dxfs count="10">
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
       <fill>
         <patternFill patternType="solid">
@@ -765,26 +785,6 @@
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
         <top style="thin">
           <color auto="1"/>
         </top>
@@ -1032,8 +1032,8 @@
     <tableColumn id="2" name="Category" dataDxfId="4"/>
     <tableColumn id="3" name="Status " dataDxfId="3"/>
     <tableColumn id="4" name="Mandate" dataDxfId="2"/>
-    <tableColumn id="5" name="Live Date" dataDxfId="0"/>
-    <tableColumn id="6" name="Update" dataDxfId="1"/>
+    <tableColumn id="5" name="Live Date" dataDxfId="1"/>
+    <tableColumn id="6" name="Update" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2187,7 +2187,7 @@
         <v>140</v>
       </c>
       <c r="E44" s="54">
-        <v>46311</v>
+        <v>46309</v>
       </c>
       <c r="F44" s="37" t="s">
         <v>141</v>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="366" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="147">
   <si>
     <t>Allocation</t>
   </si>
@@ -341,15 +341,9 @@
     <t>Data Analytics</t>
   </si>
   <si>
-    <t>Payment Portal-Back Office</t>
-  </si>
-  <si>
     <t>UBCS /Bulk</t>
   </si>
   <si>
-    <t>Raast Bulk/SPHF</t>
-  </si>
-  <si>
     <t xml:space="preserve">Business as usual. </t>
   </si>
   <si>
@@ -450,6 +444,27 @@
   </si>
   <si>
     <t>Transactions with higher amounts will be processed first, while multithreading will enable faster transaction processing.</t>
+  </si>
+  <si>
+    <t>Payment Portal-Back Office - Raast Bulk/SPHF</t>
+  </si>
+  <si>
+    <t>Both</t>
+  </si>
+  <si>
+    <t>ID locking for retired users</t>
+  </si>
+  <si>
+    <t>Zohaib Shahzad</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payment </t>
+  </si>
+  <si>
+    <t>RAAST P2P</t>
+  </si>
+  <si>
+    <t>Meeting held between CRPL , PAYSYS and Smartpay Team.</t>
   </si>
 </sst>
 </file>
@@ -488,7 +503,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -540,6 +555,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -667,7 +700,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -680,7 +713,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
@@ -693,19 +725,15 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -717,13 +745,9 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -738,12 +762,45 @@
     <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1025,8 +1082,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F64" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
-  <autoFilter ref="A1:F64"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F65" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
+  <autoFilter ref="A1:F65"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Allocation" dataDxfId="5"/>
     <tableColumn id="2" name="Category" dataDxfId="4"/>
@@ -1302,14 +1359,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="51.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.42578125" style="55" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" style="47" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="192.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1326,7 +1383,7 @@
       <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="E1" s="44" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="11" t="s">
@@ -1344,13 +1401,13 @@
         <v>44</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E2" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" s="29" t="s">
         <v>94</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1364,9 +1421,9 @@
         <v>8</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="E3" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="29" t="s">
         <v>94</v>
       </c>
       <c r="F3" s="8" t="s">
@@ -1374,22 +1431,22 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="38" t="s">
+      <c r="A4" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="16" t="s">
+      <c r="B4" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="34" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="F4" s="41" t="s">
+      <c r="E4" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4" s="36" t="s">
         <v>66</v>
       </c>
     </row>
@@ -1404,9 +1461,9 @@
         <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E5" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="E5" s="29" t="s">
         <v>94</v>
       </c>
       <c r="F5" s="7" t="s">
@@ -1421,12 +1478,12 @@
         <v>27</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="32" t="s">
+      <c r="E6" s="29" t="s">
         <v>94</v>
       </c>
       <c r="F6" s="7" t="s">
@@ -1434,410 +1491,410 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="23" t="s">
+      <c r="A7" s="22" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="24" t="s">
+      <c r="B7" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="24" t="s">
+      <c r="C7" s="23" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="46" t="s">
-        <v>94</v>
-      </c>
-      <c r="F7" s="26" t="s">
+      <c r="E7" s="40" t="s">
+        <v>94</v>
+      </c>
+      <c r="F7" s="24" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="28" t="s">
+      <c r="B8" s="26" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="28" t="s">
+      <c r="C8" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="D8" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="E8" s="45" t="s">
+        <v>94</v>
+      </c>
+      <c r="F8" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="D8" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="E8" s="52" t="s">
-        <v>94</v>
-      </c>
-      <c r="F8" s="30" t="s">
-        <v>131</v>
-      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="38" t="s">
+      <c r="A9" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="16" t="s">
+      <c r="B9" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="39" t="s">
+      <c r="D9" s="34" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="F9" s="41" t="s">
+      <c r="E9" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" s="36" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="38" t="s">
+      <c r="A10" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="16" t="s">
+      <c r="B10" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="39" t="s">
+      <c r="D10" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="F10" s="41" t="s">
+      <c r="E10" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F10" s="36" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="16" t="s">
+      <c r="B11" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="39" t="s">
+      <c r="D11" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="F11" s="41" t="s">
+      <c r="E11" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F11" s="36" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="16" t="s">
+      <c r="B12" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="39" t="s">
+      <c r="D12" s="34" t="s">
         <v>92</v>
       </c>
-      <c r="E12" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="F12" s="41" t="s">
+      <c r="E12" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F12" s="36" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="38" t="s">
+      <c r="A13" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="16" t="s">
+      <c r="B13" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="39" t="s">
+      <c r="D13" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="F13" s="41" t="s">
+      <c r="E13" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F13" s="36" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="16" t="s">
+      <c r="B14" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="39" t="s">
+      <c r="D14" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" s="41" t="s">
+      <c r="E14" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F14" s="36" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="33" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="38" t="s">
+    <row r="15" spans="1:6" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="16" t="s">
+      <c r="B15" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="39" t="s">
+      <c r="D15" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="40">
+      <c r="E15" s="35">
         <v>46218</v>
       </c>
-      <c r="F15" s="41" t="s">
+      <c r="F15" s="36" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="42" t="s">
+      <c r="A16" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="17" t="s">
+      <c r="B16" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="44" t="s">
+      <c r="C16" s="39" t="s">
         <v>80</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="17" t="s">
         <v>85</v>
       </c>
-      <c r="E16" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="F16" s="19" t="s">
+      <c r="E16" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F16" s="18" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="42" t="s">
+      <c r="A17" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="17" t="s">
+      <c r="B17" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="18" t="s">
+      <c r="D17" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="E17" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="F17" s="19" t="s">
+      <c r="E17" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F17" s="18" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="38" t="s">
+      <c r="A18" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="16" t="s">
+      <c r="B18" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="39" t="s">
+      <c r="D18" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="40">
+      <c r="E18" s="35">
         <v>46218</v>
       </c>
-      <c r="F18" s="41" t="s">
+      <c r="F18" s="36" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
+      <c r="A19" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="17" t="s">
+      <c r="B19" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="18" t="s">
+      <c r="D19" s="17" t="s">
         <v>91</v>
       </c>
-      <c r="E19" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="F19" s="43" t="s">
+      <c r="E19" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" s="38" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="38" t="s">
+      <c r="A20" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="16" t="s">
+      <c r="B20" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="39" t="s">
+      <c r="D20" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="40">
+      <c r="E20" s="35">
         <v>46220</v>
       </c>
-      <c r="F20" s="41" t="s">
+      <c r="F20" s="36" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="38" t="s">
+      <c r="A21" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="16" t="s">
+      <c r="B21" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="39" t="s">
-        <v>118</v>
-      </c>
-      <c r="E21" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="F21" s="41" t="s">
+      <c r="D21" s="34" t="s">
+        <v>116</v>
+      </c>
+      <c r="E21" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="F21" s="36" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="B22" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="D22" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="E22" s="35">
+        <v>46176</v>
+      </c>
+      <c r="F22" s="36" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="B23" s="39" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>101</v>
+      </c>
+      <c r="E23" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C24" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="E24" s="45">
+        <v>46241</v>
+      </c>
+      <c r="F24" s="28" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="45">
+        <v>46261</v>
+      </c>
+      <c r="F25" s="28" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="D26" s="27" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" s="45">
+        <v>46227</v>
+      </c>
+      <c r="F26" s="28" t="s">
         <v>121</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="38" t="s">
-        <v>6</v>
-      </c>
-      <c r="B22" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="D22" s="39" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="40">
-        <v>46176</v>
-      </c>
-      <c r="F22" s="41" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="B23" s="44" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="D23" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="E23" s="40" t="s">
-        <v>95</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="B24" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="D24" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="E24" s="52">
-        <v>46241</v>
-      </c>
-      <c r="F24" s="30" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="28" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="E25" s="52">
-        <v>46261</v>
-      </c>
-      <c r="F25" s="30" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="27" t="s">
-        <v>26</v>
-      </c>
-      <c r="B26" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="C26" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="D26" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="E26" s="52">
-        <v>46227</v>
-      </c>
-      <c r="F26" s="30" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" s="12" t="s">
         <v>7</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -1846,7 +1903,7 @@
       <c r="D27" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="32" t="s">
+      <c r="E27" s="46" t="s">
         <v>94</v>
       </c>
       <c r="F27" s="7" t="s">
@@ -1866,7 +1923,7 @@
       <c r="D28" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E28" s="53">
+      <c r="E28" s="46">
         <v>46125</v>
       </c>
       <c r="F28" s="7" t="s">
@@ -1874,22 +1931,22 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="22" t="s">
+      <c r="C29" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="14" t="s">
+      <c r="D29" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="E29" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="F29" s="15" t="s">
+      <c r="E29" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="14" t="s">
         <v>90</v>
       </c>
     </row>
@@ -1897,19 +1954,19 @@
       <c r="A30" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C30" s="13" t="s">
+      <c r="C30" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="D30" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="E30" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="F30" s="15" t="s">
+      <c r="D30" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="E30" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="F30" s="14" t="s">
         <v>100</v>
       </c>
     </row>
@@ -1926,7 +1983,7 @@
       <c r="D31" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E31" s="32" t="s">
+      <c r="E31" s="46" t="s">
         <v>94</v>
       </c>
       <c r="F31" s="7" t="s">
@@ -1946,7 +2003,7 @@
       <c r="D32" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E32" s="32">
+      <c r="E32" s="46">
         <v>46276</v>
       </c>
       <c r="F32" s="7" t="s">
@@ -1964,9 +2021,9 @@
         <v>80</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E33" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="E33" s="46" t="s">
         <v>94</v>
       </c>
       <c r="F33" s="7" t="s">
@@ -1986,7 +2043,7 @@
       <c r="D34" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E34" s="53">
+      <c r="E34" s="46">
         <v>46161</v>
       </c>
       <c r="F34" s="7" t="s">
@@ -2006,7 +2063,7 @@
       <c r="D35" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E35" s="53">
+      <c r="E35" s="46">
         <v>46147</v>
       </c>
       <c r="F35" s="7" t="s">
@@ -2026,7 +2083,7 @@
       <c r="D36" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E36" s="53">
+      <c r="E36" s="46">
         <v>46122</v>
       </c>
       <c r="F36" s="7" t="s">
@@ -2034,563 +2091,583 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="34" t="s">
+      <c r="A37" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="35" t="s">
+      <c r="B37" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="C37" s="35" t="s">
+      <c r="C37" s="53" t="s">
         <v>95</v>
       </c>
-      <c r="D37" s="36" t="s">
+      <c r="D37" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E37" s="40" t="s">
+      <c r="E37" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="F37" s="37" t="s">
-        <v>108</v>
+      <c r="F37" s="7" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="34" t="s">
+      <c r="A38" s="52" t="s">
         <v>34</v>
       </c>
-      <c r="B38" s="35" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="35" t="s">
+      <c r="B38" s="53" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="53" t="s">
         <v>95</v>
       </c>
-      <c r="D38" s="36" t="s">
+      <c r="D38" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E38" s="40" t="s">
+      <c r="E38" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="F38" s="37" t="s">
-        <v>108</v>
+      <c r="F38" s="7" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="3" t="s">
+      <c r="B39" s="55" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="55" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="56" t="s">
         <v>45</v>
       </c>
-      <c r="E39" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="F39" s="8" t="s">
+      <c r="E39" s="57" t="s">
+        <v>94</v>
+      </c>
+      <c r="F39" s="58" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B40" s="55" t="s">
         <v>27</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C40" s="55" t="s">
         <v>14</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="56" t="s">
         <v>46</v>
       </c>
-      <c r="E40" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="F40" s="8" t="s">
+      <c r="E40" s="57" t="s">
+        <v>94</v>
+      </c>
+      <c r="F40" s="58" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="3" t="s">
+      <c r="B41" s="55" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="D41" s="4" t="s">
+      <c r="D41" s="56" t="s">
         <v>48</v>
       </c>
-      <c r="E41" s="54">
+      <c r="E41" s="57">
         <v>46059</v>
       </c>
-      <c r="F41" s="8" t="s">
+      <c r="F41" s="58" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="B42" s="3" t="s">
+      <c r="B42" s="55" t="s">
         <v>38</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C42" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="D42" s="4" t="s">
+      <c r="D42" s="56" t="s">
         <v>49</v>
       </c>
-      <c r="E42" s="54">
+      <c r="E42" s="57">
         <v>46181</v>
       </c>
-      <c r="F42" s="8" t="s">
+      <c r="F42" s="58" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="3" t="s">
+      <c r="B43" s="55" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="55" t="s">
         <v>18</v>
       </c>
-      <c r="D43" s="4" t="s">
+      <c r="D43" s="56" t="s">
         <v>75</v>
       </c>
-      <c r="E43" s="54">
+      <c r="E43" s="57">
         <v>46227</v>
       </c>
-      <c r="F43" s="8" t="s">
+      <c r="F43" s="58" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="48" t="s">
+    <row r="44" spans="1:6" s="30" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="59" t="s">
         <v>65</v>
       </c>
-      <c r="B44" s="49" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="49" t="s">
+      <c r="B44" s="60" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="60" t="s">
         <v>18</v>
       </c>
-      <c r="D44" s="36" t="s">
+      <c r="D44" s="56" t="s">
+        <v>138</v>
+      </c>
+      <c r="E44" s="57">
+        <v>46309</v>
+      </c>
+      <c r="F44" s="58" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="B45" s="55" t="s">
+        <v>38</v>
+      </c>
+      <c r="C45" s="55" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="56" t="s">
+        <v>110</v>
+      </c>
+      <c r="E45" s="57" t="s">
+        <v>94</v>
+      </c>
+      <c r="F45" s="58" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="B46" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="C46" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="56" t="s">
+        <v>52</v>
+      </c>
+      <c r="E46" s="57">
+        <v>46161</v>
+      </c>
+      <c r="F46" s="58" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="B47" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" s="55" t="s">
+        <v>8</v>
+      </c>
+      <c r="D47" s="56" t="s">
+        <v>111</v>
+      </c>
+      <c r="E47" s="57" t="s">
+        <v>94</v>
+      </c>
+      <c r="F47" s="58" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="B48" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="C48" s="55" t="s">
+        <v>44</v>
+      </c>
+      <c r="D48" s="56" t="s">
+        <v>112</v>
+      </c>
+      <c r="E48" s="57" t="s">
+        <v>94</v>
+      </c>
+      <c r="F48" s="58" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="B49" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="C49" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="D49" s="56" t="s">
+        <v>53</v>
+      </c>
+      <c r="E49" s="57">
+        <v>46181</v>
+      </c>
+      <c r="F49" s="58" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="B50" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="C50" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="D50" s="56" t="s">
         <v>140</v>
       </c>
-      <c r="E44" s="54">
-        <v>46309</v>
-      </c>
-      <c r="F44" s="37" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="6" t="s">
+      <c r="E50" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="F50" s="58" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="54" t="s">
         <v>65</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C45" s="3" t="s">
+      <c r="B51" s="55" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="D51" s="56" t="s">
+        <v>105</v>
+      </c>
+      <c r="E51" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="F51" s="58" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="54" t="s">
+        <v>65</v>
+      </c>
+      <c r="B52" s="55" t="s">
+        <v>27</v>
+      </c>
+      <c r="C52" s="55" t="s">
+        <v>95</v>
+      </c>
+      <c r="D52" s="56" t="s">
+        <v>107</v>
+      </c>
+      <c r="E52" s="57" t="s">
+        <v>95</v>
+      </c>
+      <c r="F52" s="58" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="61" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="62" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="62" t="s">
+        <v>14</v>
+      </c>
+      <c r="D53" s="63" t="s">
+        <v>68</v>
+      </c>
+      <c r="E53" s="64" t="s">
+        <v>94</v>
+      </c>
+      <c r="F53" s="65" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="61" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="66" t="s">
+        <v>81</v>
+      </c>
+      <c r="C54" s="62" t="s">
         <v>8</v>
       </c>
-      <c r="D45" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="E45" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B46" s="3" t="s">
+      <c r="D54" s="63" t="s">
+        <v>82</v>
+      </c>
+      <c r="E54" s="64" t="s">
+        <v>94</v>
+      </c>
+      <c r="F54" s="65" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="67" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55" s="67" t="s">
+        <v>95</v>
+      </c>
+      <c r="D55" s="68" t="s">
+        <v>63</v>
+      </c>
+      <c r="E55" s="69" t="s">
+        <v>95</v>
+      </c>
+      <c r="F55" s="68" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="67" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56" s="67" t="s">
+        <v>104</v>
+      </c>
+      <c r="C56" s="67" t="s">
+        <v>95</v>
+      </c>
+      <c r="D56" s="68" t="s">
+        <v>104</v>
+      </c>
+      <c r="E56" s="69" t="s">
+        <v>95</v>
+      </c>
+      <c r="F56" s="68" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="70" t="s">
+        <v>57</v>
+      </c>
+      <c r="B57" s="71" t="s">
         <v>27</v>
       </c>
-      <c r="C46" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E46" s="54">
-        <v>46161</v>
-      </c>
-      <c r="F46" s="8" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B47" s="3" t="s">
+      <c r="C57" s="71" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="72" t="s">
+        <v>132</v>
+      </c>
+      <c r="E57" s="73" t="s">
+        <v>94</v>
+      </c>
+      <c r="F57" s="74" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="70" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" s="75" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="72" t="s">
+        <v>56</v>
+      </c>
+      <c r="E58" s="73" t="s">
+        <v>94</v>
+      </c>
+      <c r="F58" s="74" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="70" t="s">
+        <v>57</v>
+      </c>
+      <c r="B59" s="75" t="s">
+        <v>28</v>
+      </c>
+      <c r="C59" s="75" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="72" t="s">
+        <v>31</v>
+      </c>
+      <c r="E59" s="73" t="s">
+        <v>94</v>
+      </c>
+      <c r="F59" s="74" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="70" t="s">
+        <v>57</v>
+      </c>
+      <c r="B60" s="75" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="75" t="s">
+        <v>44</v>
+      </c>
+      <c r="D60" s="72" t="s">
+        <v>74</v>
+      </c>
+      <c r="E60" s="73" t="s">
+        <v>94</v>
+      </c>
+      <c r="F60" s="74" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="70" t="s">
+        <v>57</v>
+      </c>
+      <c r="B61" s="75" t="s">
         <v>27</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C61" s="75" t="s">
+        <v>95</v>
+      </c>
+      <c r="D61" s="72" t="s">
+        <v>60</v>
+      </c>
+      <c r="E61" s="73" t="s">
+        <v>95</v>
+      </c>
+      <c r="F61" s="74" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="41" t="s">
+        <v>133</v>
+      </c>
+      <c r="B62" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C62" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="D47" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="E47" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="F47" s="8" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C48" s="3" t="s">
+      <c r="D62" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="E62" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="F62" s="32" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="41" t="s">
+        <v>133</v>
+      </c>
+      <c r="B63" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="D48" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="E48" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="F48" s="8" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E49" s="54">
-        <v>46181</v>
-      </c>
-      <c r="F49" s="8" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E50" s="32" t="s">
-        <v>95</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="E51" s="32" t="s">
-        <v>95</v>
-      </c>
-      <c r="F51" s="8" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="E52" s="32" t="s">
-        <v>95</v>
-      </c>
-      <c r="F52" s="8" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E53" s="32" t="s">
-        <v>95</v>
-      </c>
-      <c r="F53" s="8" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D54" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="E54" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="F54" s="15" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="B55" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C55" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="D55" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="E55" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="F55" s="19" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B56" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="C56" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="D56" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="E56" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="F56" s="31" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B57" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="C57" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="D57" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="E57" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="F57" s="31" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="B58" s="47" t="s">
-        <v>27</v>
-      </c>
-      <c r="C58" s="47" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="E58" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="F58" s="41" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="B59" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="E59" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="F59" s="26" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="B60" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="C60" s="24" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="25" t="s">
-        <v>31</v>
-      </c>
-      <c r="E60" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="F60" s="26" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="B61" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="D61" s="25" t="s">
-        <v>74</v>
-      </c>
-      <c r="E61" s="32" t="s">
-        <v>94</v>
-      </c>
-      <c r="F61" s="26" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="B62" s="24" t="s">
-        <v>27</v>
-      </c>
-      <c r="C62" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="D62" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="E62" s="46" t="s">
-        <v>95</v>
-      </c>
-      <c r="F62" s="26" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="48" t="s">
-        <v>135</v>
-      </c>
-      <c r="B63" s="49" t="s">
-        <v>27</v>
-      </c>
-      <c r="C63" s="49" t="s">
-        <v>44</v>
-      </c>
-      <c r="D63" s="36" t="s">
+      <c r="D63" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="E63" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="F63" s="37" t="s">
+      <c r="E63" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="F63" s="32" t="s">
         <v>137</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="48" t="s">
+        <v>133</v>
+      </c>
+      <c r="B64" s="49" t="s">
+        <v>141</v>
+      </c>
+      <c r="C64" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="D64" s="50" t="s">
+        <v>142</v>
+      </c>
+      <c r="E64" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="F64" s="51" t="s">
         <v>135</v>
       </c>
-      <c r="B64" s="49" t="s">
-        <v>7</v>
-      </c>
-      <c r="C64" s="49" t="s">
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="48" t="s">
+        <v>143</v>
+      </c>
+      <c r="B65" s="49" t="s">
+        <v>144</v>
+      </c>
+      <c r="C65" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="D64" s="36" t="s">
-        <v>138</v>
-      </c>
-      <c r="E64" s="50" t="s">
-        <v>94</v>
-      </c>
-      <c r="F64" s="37" t="s">
-        <v>139</v>
+      <c r="D65" s="50" t="s">
+        <v>145</v>
+      </c>
+      <c r="E65" s="43" t="s">
+        <v>94</v>
+      </c>
+      <c r="F65" s="51" t="s">
+        <v>146</v>
       </c>
     </row>
   </sheetData>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="153">
   <si>
     <t>Allocation</t>
   </si>
@@ -440,9 +440,6 @@
     <t>API Shared</t>
   </si>
   <si>
-    <t xml:space="preserve">UBCS API Response </t>
-  </si>
-  <si>
     <t>Transactions with higher amounts will be processed first, while multithreading will enable faster transaction processing.</t>
   </si>
   <si>
@@ -452,9 +449,6 @@
     <t>Both</t>
   </si>
   <si>
-    <t>ID locking for retired users</t>
-  </si>
-  <si>
     <t>Zohaib Shahzad</t>
   </si>
   <si>
@@ -465,6 +459,30 @@
   </si>
   <si>
     <t>Meeting held between CRPL , PAYSYS and Smartpay Team.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rejected Transaction Alert </t>
+  </si>
+  <si>
+    <t>Email Shared With Paysys</t>
+  </si>
+  <si>
+    <t>UBCS API Late Response</t>
+  </si>
+  <si>
+    <t>NTC Advance Payment</t>
+  </si>
+  <si>
+    <t>Under UAT.</t>
+  </si>
+  <si>
+    <t>Document Management System</t>
+  </si>
+  <si>
+    <t>BRD Preparation  in Progress.</t>
+  </si>
+  <si>
+    <t>Session Expiry and User id Locking Mechanism</t>
   </si>
 </sst>
 </file>
@@ -577,7 +595,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -600,160 +618,34 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -765,113 +657,43 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="10">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right/>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="5" tint="0.59999389629810485"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
     <dxf>
       <font>
         <b/>
@@ -891,6 +713,30 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
           <bgColor theme="5" tint="0.59999389629810485"/>
         </patternFill>
       </fill>
@@ -898,20 +744,76 @@
         <left style="thin">
           <color indexed="64"/>
         </left>
+        <right/>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
         <top style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </bottom>
         <vertical style="thin">
           <color indexed="64"/>
         </vertical>
         <horizontal style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
         </horizontal>
       </border>
     </dxf>
@@ -945,16 +847,59 @@
           <color indexed="64"/>
         </right>
         <top style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </bottom>
         <vertical style="thin">
           <color indexed="64"/>
         </vertical>
         <horizontal style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="5" tint="0.59999389629810485"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
         </horizontal>
       </border>
     </dxf>
@@ -986,16 +931,16 @@
           <color indexed="64"/>
         </right>
         <top style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </top>
         <bottom style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </bottom>
         <vertical style="thin">
           <color indexed="64"/>
         </vertical>
         <horizontal style="thin">
-          <color auto="1"/>
+          <color indexed="64"/>
         </horizontal>
       </border>
     </dxf>
@@ -1027,45 +972,6 @@
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color auto="1"/>
-        </horizontal>
       </border>
     </dxf>
   </dxfs>
@@ -1082,15 +988,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F65" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
-  <autoFilter ref="A1:F65"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F68" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
+  <autoFilter ref="A1:F68"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="Allocation" dataDxfId="5"/>
-    <tableColumn id="2" name="Category" dataDxfId="4"/>
-    <tableColumn id="3" name="Status " dataDxfId="3"/>
-    <tableColumn id="4" name="Mandate" dataDxfId="2"/>
-    <tableColumn id="5" name="Live Date" dataDxfId="1"/>
-    <tableColumn id="6" name="Update" dataDxfId="0"/>
+    <tableColumn id="1" name="Allocation" dataDxfId="6"/>
+    <tableColumn id="2" name="Category" dataDxfId="5"/>
+    <tableColumn id="3" name="Status " dataDxfId="4"/>
+    <tableColumn id="4" name="Mandate" dataDxfId="3"/>
+    <tableColumn id="5" name="Live Date" dataDxfId="2"/>
+    <tableColumn id="6" name="Update" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1359,39 +1265,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="51.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.42578125" style="47" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" style="19" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="192.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="C1" s="35" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="D1" s="35" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="35" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="3" t="s">
         <v>65</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -1403,15 +1309,15 @@
       <c r="D2" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="E2" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="F2" s="8" t="s">
+      <c r="E2" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2" s="4" t="s">
         <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="3" t="s">
         <v>65</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -1423,35 +1329,35 @@
       <c r="D3" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E3" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="F3" s="8" t="s">
+      <c r="E3" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="33" t="s">
+      <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="15" t="s">
+      <c r="B4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="34" t="s">
+      <c r="D4" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="F4" s="36" t="s">
+      <c r="E4" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4" s="12" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B5" s="1" t="s">
@@ -1463,15 +1369,15 @@
       <c r="D5" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E5" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="F5" s="7" t="s">
+      <c r="E5" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -1483,495 +1389,495 @@
       <c r="D6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="29" t="s">
-        <v>94</v>
-      </c>
-      <c r="F6" s="7" t="s">
+      <c r="E6" s="9" t="s">
+        <v>94</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
+      <c r="A7" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="23" t="s">
+      <c r="B7" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="F7" s="24" t="s">
+      <c r="E7" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="F7" s="37" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="26" t="s">
+      <c r="B8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="E8" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="F8" s="28" t="s">
+      <c r="E8" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>129</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="33" t="s">
+      <c r="A9" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C9" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D9" s="34" t="s">
+      <c r="D10" s="12" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="F9" s="36" t="s">
+      <c r="E10" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="F10" s="12" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="33" t="s">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="15" t="s">
+      <c r="B11" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D10" s="34" t="s">
+      <c r="D11" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="F10" s="36" t="s">
+      <c r="E11" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="F11" s="12" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="33" t="s">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="15" t="s">
+      <c r="B12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="34" t="s">
+      <c r="D12" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="F11" s="36" t="s">
+      <c r="E12" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="F12" s="12" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="33" t="s">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="15" t="s">
+      <c r="B13" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="34" t="s">
+      <c r="D13" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="E12" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="F12" s="36" t="s">
+      <c r="E13" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="F13" s="12" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="33" t="s">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="15" t="s">
+      <c r="B14" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="34" t="s">
+      <c r="D14" s="12" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="F13" s="36" t="s">
+      <c r="E14" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="F14" s="12" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="33" t="s">
+    <row r="15" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B14" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="15" t="s">
+      <c r="B15" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="34" t="s">
+      <c r="D15" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="E14" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="F14" s="36" t="s">
+      <c r="E15" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="F15" s="12" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="15" spans="1:6" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="33" t="s">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B15" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="15" t="s">
+      <c r="B16" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="34" t="s">
+      <c r="D16" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="35">
+      <c r="E16" s="13">
         <v>46218</v>
       </c>
-      <c r="F15" s="36" t="s">
+      <c r="F16" s="12" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="37" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B17" s="38" t="s">
         <v>84</v>
       </c>
-      <c r="C16" s="39" t="s">
+      <c r="C17" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="D16" s="17" t="s">
+      <c r="D17" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="E16" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="F16" s="18" t="s">
+      <c r="E17" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="F17" s="12" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="37" t="s">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="38" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="16" t="s">
+      <c r="B18" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="17" t="s">
+      <c r="D18" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="E17" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="F17" s="18" t="s">
+      <c r="E18" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="F18" s="12" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="33" t="s">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="15" t="s">
+      <c r="B19" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="34" t="s">
+      <c r="D19" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="E18" s="35">
+      <c r="E19" s="13">
         <v>46218</v>
       </c>
-      <c r="F18" s="36" t="s">
+      <c r="F19" s="12" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="16" t="s">
+      <c r="B20" s="38" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D20" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="E19" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="F19" s="38" t="s">
+      <c r="E20" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="F20" s="34" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="33" t="s">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="15" t="s">
+      <c r="B21" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="34" t="s">
+      <c r="D21" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="E20" s="35">
+      <c r="E21" s="13">
         <v>46220</v>
       </c>
-      <c r="F20" s="36" t="s">
+      <c r="F21" s="12" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="33" t="s">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="15" t="s">
+      <c r="B22" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="34" t="s">
+      <c r="D22" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="E21" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="F21" s="36" t="s">
+      <c r="E22" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="F22" s="12" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="33" t="s">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="15" t="s">
+      <c r="B23" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="34" t="s">
+      <c r="D23" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="E22" s="35">
+      <c r="E23" s="13">
         <v>46176</v>
       </c>
-      <c r="F22" s="36" t="s">
+      <c r="F23" s="12" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="33" t="s">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B23" s="39" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="15" t="s">
+      <c r="B24" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D24" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="E23" s="35" t="s">
+      <c r="E24" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="F23" s="18" t="s">
+      <c r="F24" s="12" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="25" t="s">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="26" t="s">
+      <c r="B25" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="26" t="s">
+      <c r="C25" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="27" t="s">
+      <c r="D25" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E24" s="45">
+      <c r="E25" s="17">
         <v>46241</v>
       </c>
-      <c r="F24" s="28" t="s">
+      <c r="F25" s="8" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="25" t="s">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="26" t="s">
+      <c r="B26" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C25" s="26" t="s">
+      <c r="C26" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D25" s="27" t="s">
+      <c r="D26" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E25" s="45">
+      <c r="E26" s="17">
         <v>46261</v>
       </c>
-      <c r="F25" s="28" t="s">
+      <c r="F26" s="8" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="25" t="s">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="26" t="s">
+      <c r="B27" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="26" t="s">
+      <c r="C27" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="27" t="s">
+      <c r="D27" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E26" s="45">
+      <c r="E27" s="17">
         <v>46227</v>
       </c>
-      <c r="F26" s="28" t="s">
+      <c r="F27" s="8" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B27" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="1" t="s">
+      <c r="B28" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D28" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="46" t="s">
-        <v>94</v>
-      </c>
-      <c r="F27" s="7" t="s">
+      <c r="E28" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F28" s="2" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C29" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D29" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E28" s="46">
+      <c r="E29" s="18">
         <v>46125</v>
       </c>
-      <c r="F28" s="7" t="s">
+      <c r="F29" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="20" t="s">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="B30" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="21" t="s">
+      <c r="C30" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D30" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E29" s="46" t="s">
-        <v>94</v>
-      </c>
-      <c r="F29" s="14" t="s">
+      <c r="E30" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F30" s="2" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="D30" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="E30" s="46" t="s">
-        <v>94</v>
-      </c>
-      <c r="F30" s="14" t="s">
-        <v>100</v>
-      </c>
-    </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B31" s="1" t="s">
@@ -1983,15 +1889,15 @@
       <c r="D31" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="E31" s="46" t="s">
-        <v>94</v>
-      </c>
-      <c r="F31" s="7" t="s">
+      <c r="E31" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B32" s="1" t="s">
@@ -2003,15 +1909,15 @@
       <c r="D32" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E32" s="46">
+      <c r="E32" s="18">
         <v>46276</v>
       </c>
-      <c r="F32" s="7" t="s">
+      <c r="F32" s="2" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B33" s="1" t="s">
@@ -2023,15 +1929,15 @@
       <c r="D33" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="E33" s="46" t="s">
-        <v>94</v>
-      </c>
-      <c r="F33" s="7" t="s">
+      <c r="E33" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F33" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
@@ -2043,15 +1949,15 @@
       <c r="D34" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E34" s="46">
+      <c r="E34" s="18">
         <v>46161</v>
       </c>
-      <c r="F34" s="7" t="s">
+      <c r="F34" s="2" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B35" s="1" t="s">
@@ -2063,15 +1969,15 @@
       <c r="D35" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E35" s="46">
+      <c r="E35" s="18">
         <v>46147</v>
       </c>
-      <c r="F35" s="7" t="s">
+      <c r="F35" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B36" s="1" t="s">
@@ -2083,590 +1989,650 @@
       <c r="D36" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E36" s="46">
+      <c r="E36" s="18">
         <v>46122</v>
       </c>
-      <c r="F36" s="7" t="s">
+      <c r="F36" s="2" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="52" t="s">
+      <c r="A37" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="53" t="s">
+      <c r="B37" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C37" s="53" t="s">
+      <c r="C37" s="20" t="s">
         <v>95</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E37" s="46" t="s">
+      <c r="E37" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="F37" s="7" t="s">
+      <c r="F37" s="2" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="52" t="s">
+      <c r="A38" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B38" s="53" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="53" t="s">
+      <c r="B38" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C38" s="1" t="s">
         <v>95</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E38" s="46" t="s">
+      <c r="E38" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="F38" s="7" t="s">
+      <c r="F38" s="2" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="54" t="s">
+      <c r="A39" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B39" s="55" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="55" t="s">
+      <c r="B39" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C39" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="D39" s="56" t="s">
+      <c r="D39" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="E39" s="57" t="s">
-        <v>94</v>
-      </c>
-      <c r="F39" s="58" t="s">
+      <c r="E39" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="F39" s="22" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="54" t="s">
+      <c r="A40" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B40" s="55" t="s">
+      <c r="B40" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="C40" s="55" t="s">
+      <c r="C40" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="D40" s="56" t="s">
+      <c r="D40" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="E40" s="57" t="s">
-        <v>94</v>
-      </c>
-      <c r="F40" s="58" t="s">
+      <c r="E40" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="F40" s="22" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="54" t="s">
+      <c r="A41" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B41" s="55" t="s">
-        <v>7</v>
-      </c>
-      <c r="C41" s="55" t="s">
+      <c r="B41" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C41" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="D41" s="56" t="s">
+      <c r="D41" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="E41" s="57">
+      <c r="E41" s="23">
         <v>46059</v>
       </c>
-      <c r="F41" s="58" t="s">
+      <c r="F41" s="22" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="54" t="s">
+      <c r="A42" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B42" s="55" t="s">
+      <c r="B42" s="21" t="s">
         <v>38</v>
       </c>
-      <c r="C42" s="55" t="s">
+      <c r="C42" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="D42" s="56" t="s">
+      <c r="D42" s="22" t="s">
         <v>49</v>
       </c>
-      <c r="E42" s="57">
+      <c r="E42" s="23">
         <v>46181</v>
       </c>
-      <c r="F42" s="58" t="s">
+      <c r="F42" s="22" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="54" t="s">
+    <row r="43" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B43" s="55" t="s">
-        <v>7</v>
-      </c>
-      <c r="C43" s="55" t="s">
+      <c r="B43" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C43" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="D43" s="56" t="s">
+      <c r="D43" s="22" t="s">
         <v>75</v>
       </c>
-      <c r="E43" s="57">
+      <c r="E43" s="23">
         <v>46227</v>
       </c>
-      <c r="F43" s="58" t="s">
+      <c r="F43" s="22" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="44" spans="1:6" s="30" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="59" t="s">
+    <row r="44" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="B44" s="60" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="60" t="s">
+      <c r="B44" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="D44" s="56" t="s">
+      <c r="D44" s="22" t="s">
+        <v>147</v>
+      </c>
+      <c r="E44" s="23">
+        <v>46309</v>
+      </c>
+      <c r="F44" s="22" t="s">
         <v>138</v>
       </c>
-      <c r="E44" s="57">
-        <v>46309</v>
-      </c>
-      <c r="F44" s="58" t="s">
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B45" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C45" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D45" s="22" t="s">
+        <v>110</v>
+      </c>
+      <c r="E45" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="F45" s="22" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B46" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C46" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="22" t="s">
+        <v>52</v>
+      </c>
+      <c r="E46" s="23">
+        <v>46161</v>
+      </c>
+      <c r="F46" s="22" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="E47" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B48" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C48" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="D48" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="E48" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="F48" s="22" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B49" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C49" s="21" t="s">
+        <v>44</v>
+      </c>
+      <c r="D49" s="22" t="s">
+        <v>112</v>
+      </c>
+      <c r="E49" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="F49" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B50" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C50" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="D50" s="22" t="s">
+        <v>53</v>
+      </c>
+      <c r="E50" s="23">
+        <v>46181</v>
+      </c>
+      <c r="F50" s="22" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B51" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C51" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D51" s="22" t="s">
         <v>139</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="54" t="s">
+      <c r="E51" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="F51" s="22" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B45" s="55" t="s">
-        <v>38</v>
-      </c>
-      <c r="C45" s="55" t="s">
+      <c r="B52" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C52" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D52" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="E52" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="F52" s="22" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C53" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="D53" s="22" t="s">
+        <v>107</v>
+      </c>
+      <c r="E53" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="F53" s="22" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="26" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="E54" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="F54" s="39" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="40" t="s">
+        <v>81</v>
+      </c>
+      <c r="C55" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D45" s="56" t="s">
-        <v>110</v>
-      </c>
-      <c r="E45" s="57" t="s">
-        <v>94</v>
-      </c>
-      <c r="F45" s="58" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="54" t="s">
-        <v>65</v>
-      </c>
-      <c r="B46" s="55" t="s">
+      <c r="D55" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="E55" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="F55" s="39" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56" s="26" t="s">
+        <v>62</v>
+      </c>
+      <c r="C56" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="D56" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="E56" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="F56" s="27" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="26" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="C57" s="26" t="s">
+        <v>95</v>
+      </c>
+      <c r="D57" s="27" t="s">
+        <v>104</v>
+      </c>
+      <c r="E57" s="28" t="s">
+        <v>95</v>
+      </c>
+      <c r="F57" s="27" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="C46" s="55" t="s">
-        <v>18</v>
-      </c>
-      <c r="D46" s="56" t="s">
-        <v>52</v>
-      </c>
-      <c r="E46" s="57">
-        <v>46161</v>
-      </c>
-      <c r="F46" s="58" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="54" t="s">
-        <v>65</v>
-      </c>
-      <c r="B47" s="55" t="s">
+      <c r="C58" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="30" t="s">
+        <v>132</v>
+      </c>
+      <c r="E58" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="F58" s="30" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B59" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="30" t="s">
+        <v>56</v>
+      </c>
+      <c r="E59" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="F59" s="30" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B60" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="C60" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="D60" s="30" t="s">
+        <v>31</v>
+      </c>
+      <c r="E60" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="F60" s="30" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B61" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C61" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="D61" s="30" t="s">
+        <v>74</v>
+      </c>
+      <c r="E61" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="F61" s="30" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B62" s="32" t="s">
         <v>27</v>
       </c>
-      <c r="C47" s="55" t="s">
+      <c r="C62" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="D62" s="30" t="s">
+        <v>60</v>
+      </c>
+      <c r="E62" s="31" t="s">
+        <v>95</v>
+      </c>
+      <c r="F62" s="30" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C63" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D47" s="56" t="s">
-        <v>111</v>
-      </c>
-      <c r="E47" s="57" t="s">
-        <v>94</v>
-      </c>
-      <c r="F47" s="58" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="54" t="s">
-        <v>65</v>
-      </c>
-      <c r="B48" s="55" t="s">
+      <c r="D63" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E63" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F63" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="B64" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D64" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="E64" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F64" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="B65" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="E65" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F65" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="B66" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>143</v>
+      </c>
+      <c r="E66" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F66" s="11" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="B67" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C48" s="55" t="s">
+      <c r="C67" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D48" s="56" t="s">
-        <v>112</v>
-      </c>
-      <c r="E48" s="57" t="s">
-        <v>94</v>
-      </c>
-      <c r="F48" s="58" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="54" t="s">
-        <v>65</v>
-      </c>
-      <c r="B49" s="55" t="s">
+      <c r="D67" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E67" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="33" t="s">
+        <v>141</v>
+      </c>
+      <c r="B68" s="33" t="s">
         <v>27</v>
       </c>
-      <c r="C49" s="55" t="s">
-        <v>18</v>
-      </c>
-      <c r="D49" s="56" t="s">
-        <v>53</v>
-      </c>
-      <c r="E49" s="57">
-        <v>46181</v>
-      </c>
-      <c r="F49" s="58" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="54" t="s">
-        <v>65</v>
-      </c>
-      <c r="B50" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="C50" s="55" t="s">
-        <v>95</v>
-      </c>
-      <c r="D50" s="56" t="s">
-        <v>140</v>
-      </c>
-      <c r="E50" s="57" t="s">
-        <v>95</v>
-      </c>
-      <c r="F50" s="58" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="54" t="s">
-        <v>65</v>
-      </c>
-      <c r="B51" s="55" t="s">
-        <v>7</v>
-      </c>
-      <c r="C51" s="55" t="s">
-        <v>95</v>
-      </c>
-      <c r="D51" s="56" t="s">
-        <v>105</v>
-      </c>
-      <c r="E51" s="57" t="s">
-        <v>95</v>
-      </c>
-      <c r="F51" s="58" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="54" t="s">
-        <v>65</v>
-      </c>
-      <c r="B52" s="55" t="s">
-        <v>27</v>
-      </c>
-      <c r="C52" s="55" t="s">
-        <v>95</v>
-      </c>
-      <c r="D52" s="56" t="s">
-        <v>107</v>
-      </c>
-      <c r="E52" s="57" t="s">
-        <v>95</v>
-      </c>
-      <c r="F52" s="58" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="61" t="s">
-        <v>61</v>
-      </c>
-      <c r="B53" s="62" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="62" t="s">
-        <v>14</v>
-      </c>
-      <c r="D53" s="63" t="s">
-        <v>68</v>
-      </c>
-      <c r="E53" s="64" t="s">
-        <v>94</v>
-      </c>
-      <c r="F53" s="65" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="61" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="66" t="s">
-        <v>81</v>
-      </c>
-      <c r="C54" s="62" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="63" t="s">
-        <v>82</v>
-      </c>
-      <c r="E54" s="64" t="s">
-        <v>94</v>
-      </c>
-      <c r="F54" s="65" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="67" t="s">
-        <v>61</v>
-      </c>
-      <c r="B55" s="67" t="s">
-        <v>62</v>
-      </c>
-      <c r="C55" s="67" t="s">
-        <v>95</v>
-      </c>
-      <c r="D55" s="68" t="s">
-        <v>63</v>
-      </c>
-      <c r="E55" s="69" t="s">
-        <v>95</v>
-      </c>
-      <c r="F55" s="68" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="67" t="s">
-        <v>61</v>
-      </c>
-      <c r="B56" s="67" t="s">
-        <v>104</v>
-      </c>
-      <c r="C56" s="67" t="s">
-        <v>95</v>
-      </c>
-      <c r="D56" s="68" t="s">
-        <v>104</v>
-      </c>
-      <c r="E56" s="69" t="s">
-        <v>95</v>
-      </c>
-      <c r="F56" s="68" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="B57" s="71" t="s">
-        <v>27</v>
-      </c>
-      <c r="C57" s="71" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="72" t="s">
-        <v>132</v>
-      </c>
-      <c r="E57" s="73" t="s">
-        <v>94</v>
-      </c>
-      <c r="F57" s="74" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="B58" s="75" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="72" t="s">
-        <v>56</v>
-      </c>
-      <c r="E58" s="73" t="s">
-        <v>94</v>
-      </c>
-      <c r="F58" s="74" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="B59" s="75" t="s">
-        <v>28</v>
-      </c>
-      <c r="C59" s="75" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" s="72" t="s">
-        <v>31</v>
-      </c>
-      <c r="E59" s="73" t="s">
-        <v>94</v>
-      </c>
-      <c r="F59" s="74" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="B60" s="75" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="75" t="s">
+      <c r="C68" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D60" s="72" t="s">
-        <v>74</v>
-      </c>
-      <c r="E60" s="73" t="s">
-        <v>94</v>
-      </c>
-      <c r="F60" s="74" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="70" t="s">
-        <v>57</v>
-      </c>
-      <c r="B61" s="75" t="s">
-        <v>27</v>
-      </c>
-      <c r="C61" s="75" t="s">
-        <v>95</v>
-      </c>
-      <c r="D61" s="72" t="s">
-        <v>60</v>
-      </c>
-      <c r="E61" s="73" t="s">
-        <v>95</v>
-      </c>
-      <c r="F61" s="74" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="41" t="s">
-        <v>133</v>
-      </c>
-      <c r="B62" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="C62" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="D62" s="31" t="s">
-        <v>134</v>
-      </c>
-      <c r="E62" s="43" t="s">
-        <v>94</v>
-      </c>
-      <c r="F62" s="32" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="41" t="s">
-        <v>133</v>
-      </c>
-      <c r="B63" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="D63" s="31" t="s">
-        <v>136</v>
-      </c>
-      <c r="E63" s="43" t="s">
-        <v>94</v>
-      </c>
-      <c r="F63" s="32" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="48" t="s">
-        <v>133</v>
-      </c>
-      <c r="B64" s="49" t="s">
-        <v>141</v>
-      </c>
-      <c r="C64" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="D64" s="50" t="s">
-        <v>142</v>
-      </c>
-      <c r="E64" s="43" t="s">
-        <v>94</v>
-      </c>
-      <c r="F64" s="51" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="48" t="s">
-        <v>143</v>
-      </c>
-      <c r="B65" s="49" t="s">
-        <v>144</v>
-      </c>
-      <c r="C65" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="D65" s="50" t="s">
+      <c r="D68" s="41" t="s">
         <v>145</v>
       </c>
-      <c r="E65" s="43" t="s">
-        <v>94</v>
-      </c>
-      <c r="F65" s="51" t="s">
+      <c r="E68" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F68" s="41" t="s">
         <v>146</v>
       </c>
     </row>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="390" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="150">
   <si>
     <t>Allocation</t>
   </si>
@@ -407,9 +407,6 @@
     <t>HR Salary-Purpose IBT</t>
   </si>
   <si>
-    <t>Scoping</t>
-  </si>
-  <si>
     <t>Govt Salaries &amp; Pension (Putty)</t>
   </si>
   <si>
@@ -440,9 +437,6 @@
     <t>API Shared</t>
   </si>
   <si>
-    <t>Transactions with higher amounts will be processed first, while multithreading will enable faster transaction processing.</t>
-  </si>
-  <si>
     <t>Payment Portal-Back Office - Raast Bulk/SPHF</t>
   </si>
   <si>
@@ -465,9 +459,6 @@
   </si>
   <si>
     <t>Email Shared With Paysys</t>
-  </si>
-  <si>
-    <t>UBCS API Late Response</t>
   </si>
   <si>
     <t>NTC Advance Payment</t>
@@ -622,7 +613,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -663,7 +654,6 @@
     <xf numFmtId="14" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -695,45 +685,6 @@
   </cellStyles>
   <dxfs count="10">
     <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -974,6 +925,45 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -988,15 +978,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F68" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="9" tableBorderDxfId="8" totalsRowBorderDxfId="7">
-  <autoFilter ref="A1:F68"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F67" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
+  <autoFilter ref="A1:F67"/>
   <tableColumns count="6">
-    <tableColumn id="1" name="Allocation" dataDxfId="6"/>
-    <tableColumn id="2" name="Category" dataDxfId="5"/>
-    <tableColumn id="3" name="Status " dataDxfId="4"/>
-    <tableColumn id="4" name="Mandate" dataDxfId="3"/>
-    <tableColumn id="5" name="Live Date" dataDxfId="2"/>
-    <tableColumn id="6" name="Update" dataDxfId="1"/>
+    <tableColumn id="1" name="Allocation" dataDxfId="5"/>
+    <tableColumn id="2" name="Category" dataDxfId="4"/>
+    <tableColumn id="3" name="Status " dataDxfId="3"/>
+    <tableColumn id="4" name="Mandate" dataDxfId="2"/>
+    <tableColumn id="5" name="Live Date" dataDxfId="1"/>
+    <tableColumn id="6" name="Update" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1265,7 +1255,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
@@ -1277,22 +1267,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="34" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1313,7 +1303,7 @@
         <v>94</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1337,23 +1327,23 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>66</v>
+      <c r="A4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1412,7 +1402,7 @@
       <c r="E7" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="F7" s="37" t="s">
+      <c r="F7" s="36" t="s">
         <v>59</v>
       </c>
     </row>
@@ -1424,36 +1414,36 @@
         <v>27</v>
       </c>
       <c r="C8" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="E8" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="E8" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>129</v>
-      </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="F9" s="11" t="s">
-        <v>149</v>
+      <c r="D9" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1464,16 +1454,16 @@
         <v>7</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D10" s="12" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E10" s="13" t="s">
         <v>94</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>67</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -1484,56 +1474,56 @@
         <v>7</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>94</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>66</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="15" t="s">
         <v>6</v>
       </c>
       <c r="B12" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>13</v>
+      <c r="D12" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>7</v>
+      <c r="B13" s="37" t="s">
+        <v>84</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="E13" s="13" t="s">
         <v>94</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1544,19 +1534,19 @@
         <v>7</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="E14" s="13" t="s">
         <v>94</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>6</v>
       </c>
@@ -1567,13 +1557,13 @@
         <v>18</v>
       </c>
       <c r="D15" s="12" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E15" s="13" t="s">
         <v>94</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>97</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1587,53 +1577,53 @@
         <v>18</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="13">
-        <v>46218</v>
+        <v>10</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>94</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>20</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="38" t="s">
+      <c r="A17" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B17" s="38" t="s">
-        <v>84</v>
+      <c r="B17" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="E17" s="13" t="s">
         <v>94</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="38" t="s">
+      <c r="A18" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B18" s="38" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="38" t="s">
+      <c r="B18" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>18</v>
       </c>
       <c r="D18" s="12" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="E18" s="13" t="s">
         <v>94</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1647,32 +1637,32 @@
         <v>18</v>
       </c>
       <c r="D19" s="12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E19" s="13">
         <v>46218</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="B20" s="38" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="38" t="s">
+      <c r="B20" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="37" t="s">
         <v>18</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E20" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="F20" s="34" t="s">
+      <c r="F20" s="12" t="s">
         <v>73</v>
       </c>
     </row>
@@ -1687,33 +1677,33 @@
         <v>18</v>
       </c>
       <c r="D21" s="12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E21" s="13">
-        <v>46220</v>
+        <v>46218</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>8</v>
+      <c r="B22" s="37" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="37" t="s">
+        <v>18</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="F22" s="12" t="s">
-        <v>119</v>
+      <c r="F22" s="33" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1727,53 +1717,53 @@
         <v>18</v>
       </c>
       <c r="D23" s="12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E23" s="13">
-        <v>46176</v>
+        <v>46220</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>98</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D24" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="E24" s="13">
+        <v>46176</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="5" t="s">
+      <c r="B25" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="D25" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="E24" s="13" t="s">
+      <c r="E25" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="F25" s="12" t="s">
         <v>106</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B25" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E25" s="17">
-        <v>46241</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1787,13 +1777,13 @@
         <v>18</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E26" s="17">
-        <v>46261</v>
+        <v>46241</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1801,79 +1791,79 @@
         <v>26</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>18</v>
       </c>
       <c r="D27" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="17">
+        <v>46261</v>
+      </c>
+      <c r="F27" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="E27" s="17">
+      <c r="E28" s="17">
         <v>46227</v>
       </c>
-      <c r="F27" s="8" t="s">
+      <c r="F28" s="8" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E28" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
+      <c r="B29" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E29" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B30" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E29" s="18">
-        <v>46125</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" s="20" t="s">
-        <v>8</v>
+      <c r="C30" s="1" t="s">
+        <v>80</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="E30" s="18" t="s">
         <v>94</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1887,13 +1877,13 @@
         <v>80</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="E31" s="18" t="s">
         <v>94</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>93</v>
+        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1907,13 +1897,13 @@
         <v>18</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="E32" s="18">
-        <v>46276</v>
+        <v>46125</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1924,16 +1914,16 @@
         <v>27</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>94</v>
+        <v>36</v>
+      </c>
+      <c r="E33" s="18">
+        <v>46276</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>37</v>
+        <v>93</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1956,7 +1946,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
@@ -1996,7 +1986,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="20" t="s">
         <v>34</v>
       </c>
@@ -2037,23 +2027,23 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="21" t="s">
+      <c r="A39" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="B39" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C39" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="D39" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="E39" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="F39" s="22" t="s">
-        <v>76</v>
+      <c r="B39" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>148</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
@@ -2064,16 +2054,16 @@
         <v>27</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="D40" s="22" t="s">
-        <v>46</v>
+        <v>112</v>
       </c>
       <c r="E40" s="23" t="s">
         <v>94</v>
       </c>
       <c r="F40" s="22" t="s">
-        <v>77</v>
+        <v>130</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
@@ -2081,19 +2071,19 @@
         <v>65</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D41" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="E41" s="23">
-        <v>46059</v>
+        <v>110</v>
+      </c>
+      <c r="E41" s="23" t="s">
+        <v>94</v>
       </c>
       <c r="F41" s="22" t="s">
-        <v>78</v>
+        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2101,59 +2091,59 @@
         <v>65</v>
       </c>
       <c r="B42" s="21" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D42" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="E42" s="23">
-        <v>46181</v>
+        <v>111</v>
+      </c>
+      <c r="E42" s="23" t="s">
+        <v>94</v>
       </c>
       <c r="F42" s="22" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="21" t="s">
         <v>65</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D43" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E43" s="23">
-        <v>46227</v>
+        <v>46</v>
+      </c>
+      <c r="E43" s="23" t="s">
+        <v>94</v>
       </c>
       <c r="F43" s="22" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="24" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B44" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="C44" s="24" t="s">
-        <v>18</v>
+      <c r="B44" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="21" t="s">
+        <v>80</v>
       </c>
       <c r="D44" s="22" t="s">
-        <v>147</v>
-      </c>
-      <c r="E44" s="23">
-        <v>46309</v>
+        <v>45</v>
+      </c>
+      <c r="E44" s="23" t="s">
+        <v>94</v>
       </c>
       <c r="F44" s="22" t="s">
-        <v>138</v>
+        <v>76</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2161,59 +2151,59 @@
         <v>65</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D45" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="E45" s="23" t="s">
-        <v>94</v>
+        <v>48</v>
+      </c>
+      <c r="E45" s="23">
+        <v>46059</v>
       </c>
       <c r="F45" s="22" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="21" t="s">
         <v>65</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C46" s="21" t="s">
         <v>18</v>
       </c>
       <c r="D46" s="22" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E46" s="23">
-        <v>46161</v>
+        <v>46181</v>
       </c>
       <c r="F46" s="22" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="B47" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C47" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D47" s="11" t="s">
-        <v>150</v>
-      </c>
-      <c r="E47" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="F47" s="11" t="s">
-        <v>151</v>
+      <c r="B47" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="21" t="s">
+        <v>18</v>
+      </c>
+      <c r="D47" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E47" s="23">
+        <v>46227</v>
+      </c>
+      <c r="F47" s="22" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2224,16 +2214,16 @@
         <v>27</v>
       </c>
       <c r="C48" s="21" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="D48" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="E48" s="23" t="s">
-        <v>94</v>
+        <v>52</v>
+      </c>
+      <c r="E48" s="23">
+        <v>46161</v>
       </c>
       <c r="F48" s="22" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2244,16 +2234,16 @@
         <v>27</v>
       </c>
       <c r="C49" s="21" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="D49" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="E49" s="23" t="s">
-        <v>94</v>
+        <v>53</v>
+      </c>
+      <c r="E49" s="23">
+        <v>46181</v>
       </c>
       <c r="F49" s="22" t="s">
-        <v>131</v>
+        <v>79</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2264,16 +2254,16 @@
         <v>27</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>18</v>
+        <v>95</v>
       </c>
       <c r="D50" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="E50" s="23">
-        <v>46181</v>
+        <v>137</v>
+      </c>
+      <c r="E50" s="23" t="s">
+        <v>95</v>
       </c>
       <c r="F50" s="22" t="s">
-        <v>79</v>
+        <v>106</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2281,13 +2271,13 @@
         <v>65</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C51" s="21" t="s">
         <v>95</v>
       </c>
       <c r="D51" s="22" t="s">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="E51" s="23" t="s">
         <v>95</v>
@@ -2301,13 +2291,13 @@
         <v>65</v>
       </c>
       <c r="B52" s="21" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C52" s="21" t="s">
         <v>95</v>
       </c>
       <c r="D52" s="22" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E52" s="23" t="s">
         <v>95</v>
@@ -2317,248 +2307,248 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B53" s="21" t="s">
+      <c r="A53" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="39" t="s">
+        <v>81</v>
+      </c>
+      <c r="C53" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="E53" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="F53" s="38" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="E54" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="F54" s="38" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="D55" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="E55" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="F55" s="26" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="C56" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="D56" s="26" t="s">
+        <v>104</v>
+      </c>
+      <c r="E56" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="F56" s="26" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B57" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="C53" s="21" t="s">
+      <c r="C57" s="28" t="s">
+        <v>8</v>
+      </c>
+      <c r="D57" s="29" t="s">
+        <v>131</v>
+      </c>
+      <c r="E57" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="F57" s="29" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="E58" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="F58" s="29" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B59" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C59" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="E59" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="F59" s="29" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B60" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D60" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="E60" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="F60" s="29" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B61" s="31" t="s">
+        <v>27</v>
+      </c>
+      <c r="C61" s="31" t="s">
         <v>95</v>
       </c>
-      <c r="D53" s="22" t="s">
-        <v>107</v>
-      </c>
-      <c r="E53" s="23" t="s">
+      <c r="D61" s="29" t="s">
+        <v>60</v>
+      </c>
+      <c r="E61" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="F53" s="22" t="s">
+      <c r="F61" s="29" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="26" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="D54" s="39" t="s">
-        <v>68</v>
-      </c>
-      <c r="E54" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="F54" s="39" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="B55" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="C55" s="26" t="s">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="15" t="s">
+        <v>132</v>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C62" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D55" s="39" t="s">
-        <v>82</v>
-      </c>
-      <c r="E55" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="F55" s="39" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="B56" s="26" t="s">
-        <v>62</v>
-      </c>
-      <c r="C56" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="D56" s="27" t="s">
-        <v>63</v>
-      </c>
-      <c r="E56" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="F56" s="27" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="26" t="s">
-        <v>61</v>
-      </c>
-      <c r="B57" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="C57" s="26" t="s">
-        <v>95</v>
-      </c>
-      <c r="D57" s="27" t="s">
-        <v>104</v>
-      </c>
-      <c r="E57" s="28" t="s">
-        <v>95</v>
-      </c>
-      <c r="F57" s="27" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="B58" s="29" t="s">
-        <v>27</v>
-      </c>
-      <c r="C58" s="29" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="30" t="s">
-        <v>132</v>
-      </c>
-      <c r="E58" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="F58" s="30" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="B59" s="32" t="s">
-        <v>7</v>
-      </c>
-      <c r="C59" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" s="30" t="s">
-        <v>56</v>
-      </c>
-      <c r="E59" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="F59" s="30" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="B60" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="C60" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="E60" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="F60" s="30" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="B61" s="32" t="s">
-        <v>7</v>
-      </c>
-      <c r="C61" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="D61" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="E61" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="F61" s="30" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="B62" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C62" s="32" t="s">
-        <v>95</v>
-      </c>
-      <c r="D62" s="30" t="s">
-        <v>60</v>
-      </c>
-      <c r="E62" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="F62" s="30" t="s">
-        <v>106</v>
+      <c r="D62" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="E62" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F62" s="11" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="D63" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E63" s="16" t="s">
         <v>94</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="15" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>7</v>
+        <v>138</v>
       </c>
       <c r="C64" s="15" t="s">
         <v>44</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>136</v>
+        <v>149</v>
       </c>
       <c r="E64" s="16" t="s">
         <v>94</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="15" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B65" s="15" t="s">
         <v>140</v>
@@ -2567,73 +2557,53 @@
         <v>44</v>
       </c>
       <c r="D65" s="11" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="E65" s="16" t="s">
         <v>94</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="15" t="s">
-        <v>141</v>
-      </c>
-      <c r="B66" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="C66" s="15" t="s">
+      <c r="A66" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C66" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D66" s="11" t="s">
-        <v>143</v>
-      </c>
-      <c r="E66" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="F66" s="11" t="s">
-        <v>144</v>
+      <c r="D66" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E66" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="B67" s="1" t="s">
+      <c r="A67" s="32" t="s">
+        <v>139</v>
+      </c>
+      <c r="B67" s="32" t="s">
         <v>27</v>
       </c>
       <c r="C67" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D67" s="2" t="s">
-        <v>114</v>
+      <c r="D67" s="40" t="s">
+        <v>143</v>
       </c>
       <c r="E67" s="18" t="s">
         <v>94</v>
       </c>
-      <c r="F67" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="33" t="s">
-        <v>141</v>
-      </c>
-      <c r="B68" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="C68" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D68" s="41" t="s">
-        <v>145</v>
-      </c>
-      <c r="E68" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="F68" s="41" t="s">
-        <v>146</v>
+      <c r="F67" s="40" t="s">
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="385" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="155">
   <si>
     <t>Allocation</t>
   </si>
@@ -284,9 +284,6 @@
     <t>Admin MGMT</t>
   </si>
   <si>
-    <t>UAT Done.</t>
-  </si>
-  <si>
     <t>E Stamping Sindh</t>
   </si>
   <si>
@@ -474,6 +471,24 @@
   </si>
   <si>
     <t>Session Expiry and User id Locking Mechanism</t>
+  </si>
+  <si>
+    <t>RAAST Bulk Debit Reverse</t>
+  </si>
+  <si>
+    <t>Paysys is working on it</t>
+  </si>
+  <si>
+    <t>Title fetch while re attempting</t>
+  </si>
+  <si>
+    <t>BISE DI Khan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Live </t>
+  </si>
+  <si>
+    <t>UAT Done, CMC</t>
   </si>
 </sst>
 </file>
@@ -586,7 +601,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -609,11 +624,46 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -679,6 +729,13 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -904,15 +961,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -920,6 +968,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -978,8 +1035,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F67" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
-  <autoFilter ref="A1:F67"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:F70" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="7" tableBorderDxfId="8" totalsRowBorderDxfId="6">
+  <autoFilter ref="A1:F70"/>
   <tableColumns count="6">
     <tableColumn id="1" name="Allocation" dataDxfId="5"/>
     <tableColumn id="2" name="Category" dataDxfId="4"/>
@@ -1255,7 +1312,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
@@ -1297,13 +1354,13 @@
         <v>44</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1317,10 +1374,10 @@
         <v>8</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F3" s="4" t="s">
         <v>47</v>
@@ -1340,10 +1397,10 @@
         <v>70</v>
       </c>
       <c r="E4" s="18" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -1357,13 +1414,13 @@
         <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -1380,7 +1437,7 @@
         <v>54</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>55</v>
@@ -1400,7 +1457,7 @@
         <v>58</v>
       </c>
       <c r="E7" s="14" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F7" s="36" t="s">
         <v>59</v>
@@ -1417,13 +1474,13 @@
         <v>44</v>
       </c>
       <c r="D8" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="F8" s="8" t="s">
         <v>127</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1437,13 +1494,13 @@
         <v>8</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1460,7 +1517,7 @@
         <v>12</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F10" s="12" t="s">
         <v>13</v>
@@ -1480,7 +1537,7 @@
         <v>15</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F11" s="12" t="s">
         <v>16</v>
@@ -1497,13 +1554,13 @@
         <v>8</v>
       </c>
       <c r="D12" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F12" s="11" t="s">
         <v>145</v>
-      </c>
-      <c r="E12" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -1520,10 +1577,10 @@
         <v>85</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>86</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1540,10 +1597,10 @@
         <v>11</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>66</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1560,7 +1617,7 @@
         <v>9</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F15" s="12" t="s">
         <v>67</v>
@@ -1580,7 +1637,7 @@
         <v>10</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F16" s="12" t="s">
         <v>66</v>
@@ -1597,13 +1654,13 @@
         <v>18</v>
       </c>
       <c r="D17" s="12" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1620,10 +1677,10 @@
         <v>17</v>
       </c>
       <c r="E18" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1657,10 +1714,10 @@
         <v>18</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E20" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F20" s="12" t="s">
         <v>73</v>
@@ -1697,10 +1754,10 @@
         <v>18</v>
       </c>
       <c r="D22" s="12" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F22" s="33" t="s">
         <v>73</v>
@@ -1743,27 +1800,27 @@
         <v>46176</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E25" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1783,7 +1840,7 @@
         <v>46241</v>
       </c>
       <c r="F26" s="8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1803,7 +1860,7 @@
         <v>46261</v>
       </c>
       <c r="F27" s="8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -1823,67 +1880,67 @@
         <v>46227</v>
       </c>
       <c r="F28" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="20" t="s">
+      <c r="A29" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="20" t="s">
+      <c r="B29" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="20" t="s">
+      <c r="C29" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="D29" s="43" t="s">
+        <v>149</v>
+      </c>
+      <c r="E29" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="F29" s="45" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="41" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="42" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="D30" s="43" t="s">
+        <v>151</v>
+      </c>
+      <c r="E30" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="F30" s="45" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C31" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D31" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E31" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="F31" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="E29" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E30" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1897,13 +1954,13 @@
         <v>18</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>72</v>
+        <v>35</v>
       </c>
       <c r="E32" s="18">
-        <v>46125</v>
+        <v>46318</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1914,16 +1971,16 @@
         <v>27</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E33" s="18">
-        <v>46276</v>
+        <v>114</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>93</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>93</v>
+        <v>37</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1937,13 +1994,13 @@
         <v>18</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E34" s="18">
-        <v>46161</v>
+        <v>46125</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
@@ -1957,13 +2014,13 @@
         <v>18</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="E35" s="18">
-        <v>46147</v>
+        <v>46276</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>41</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -1977,113 +2034,113 @@
         <v>18</v>
       </c>
       <c r="D36" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E36" s="18">
+        <v>46161</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E37" s="18">
+        <v>46147</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E36" s="18">
+      <c r="E38" s="18">
         <v>46122</v>
       </c>
-      <c r="F36" s="2" t="s">
+      <c r="F38" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="20" t="s">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="B37" s="20" t="s">
+      <c r="B39" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C37" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="D37" s="2" t="s">
+      <c r="C39" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="E37" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="B38" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="15" t="s">
+      <c r="E40" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="B41" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C41" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D39" s="11" t="s">
+      <c r="D41" s="11" t="s">
+        <v>146</v>
+      </c>
+      <c r="E41" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F41" s="11" t="s">
         <v>147</v>
-      </c>
-      <c r="E39" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="F39" s="11" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B40" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C40" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="D40" s="22" t="s">
-        <v>112</v>
-      </c>
-      <c r="E40" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="F40" s="22" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B41" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C41" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="E41" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="F41" s="22" t="s">
-        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -2094,16 +2151,16 @@
         <v>27</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="D42" s="22" t="s">
         <v>111</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F42" s="22" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -2111,19 +2168,19 @@
         <v>65</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D43" s="22" t="s">
-        <v>46</v>
+        <v>109</v>
       </c>
       <c r="E43" s="23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F43" s="22" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -2131,19 +2188,19 @@
         <v>65</v>
       </c>
       <c r="B44" s="21" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>80</v>
+        <v>8</v>
       </c>
       <c r="D44" s="22" t="s">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="E44" s="23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F44" s="22" t="s">
-        <v>76</v>
+        <v>124</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -2151,19 +2208,19 @@
         <v>65</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D45" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="E45" s="23">
-        <v>46059</v>
+        <v>46</v>
+      </c>
+      <c r="E45" s="23" t="s">
+        <v>93</v>
       </c>
       <c r="F45" s="22" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -2171,19 +2228,19 @@
         <v>65</v>
       </c>
       <c r="B46" s="21" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="C46" s="21" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="D46" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="E46" s="23">
-        <v>46181</v>
+        <v>45</v>
+      </c>
+      <c r="E46" s="23" t="s">
+        <v>93</v>
       </c>
       <c r="F46" s="22" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -2197,13 +2254,13 @@
         <v>18</v>
       </c>
       <c r="D47" s="22" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="E47" s="23">
-        <v>46227</v>
+        <v>46059</v>
       </c>
       <c r="F47" s="22" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
@@ -2211,19 +2268,19 @@
         <v>65</v>
       </c>
       <c r="B48" s="21" t="s">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="C48" s="21" t="s">
         <v>18</v>
       </c>
       <c r="D48" s="22" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E48" s="23">
-        <v>46161</v>
+        <v>46181</v>
       </c>
       <c r="F48" s="22" t="s">
-        <v>124</v>
+        <v>50</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -2231,19 +2288,19 @@
         <v>65</v>
       </c>
       <c r="B49" s="21" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C49" s="21" t="s">
         <v>18</v>
       </c>
       <c r="D49" s="22" t="s">
-        <v>53</v>
+        <v>75</v>
       </c>
       <c r="E49" s="23">
-        <v>46181</v>
+        <v>46227</v>
       </c>
       <c r="F49" s="22" t="s">
-        <v>79</v>
+        <v>51</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -2254,16 +2311,16 @@
         <v>27</v>
       </c>
       <c r="C50" s="21" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="D50" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="E50" s="23" t="s">
-        <v>95</v>
+        <v>52</v>
+      </c>
+      <c r="E50" s="23">
+        <v>46161</v>
       </c>
       <c r="F50" s="22" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -2271,19 +2328,19 @@
         <v>65</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>95</v>
+        <v>18</v>
       </c>
       <c r="D51" s="22" t="s">
-        <v>105</v>
-      </c>
-      <c r="E51" s="23" t="s">
-        <v>95</v>
+        <v>53</v>
+      </c>
+      <c r="E51" s="23">
+        <v>46181</v>
       </c>
       <c r="F51" s="22" t="s">
-        <v>106</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -2294,76 +2351,76 @@
         <v>27</v>
       </c>
       <c r="C52" s="21" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D52" s="22" t="s">
-        <v>107</v>
+        <v>136</v>
       </c>
       <c r="E52" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F52" s="22" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B53" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C53" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="D53" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="E53" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="F53" s="22" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="B54" s="21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C54" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="D54" s="22" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="B53" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="C53" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D53" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="E53" s="24" t="s">
+      <c r="E54" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="F53" s="38" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C54" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D54" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="E54" s="24" t="s">
-        <v>94</v>
-      </c>
-      <c r="F54" s="38" t="s">
-        <v>69</v>
+      <c r="F54" s="22" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="25" t="s">
         <v>61</v>
       </c>
-      <c r="B55" s="25" t="s">
-        <v>62</v>
+      <c r="B55" s="39" t="s">
+        <v>81</v>
       </c>
       <c r="C55" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="D55" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="E55" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="F55" s="26" t="s">
-        <v>64</v>
+        <v>8</v>
+      </c>
+      <c r="D55" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="E55" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="F55" s="38" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -2371,76 +2428,76 @@
         <v>61</v>
       </c>
       <c r="B56" s="25" t="s">
-        <v>104</v>
+        <v>7</v>
       </c>
       <c r="C56" s="25" t="s">
-        <v>95</v>
-      </c>
-      <c r="D56" s="26" t="s">
-        <v>104</v>
-      </c>
-      <c r="E56" s="27" t="s">
-        <v>95</v>
-      </c>
-      <c r="F56" s="26" t="s">
-        <v>106</v>
+        <v>14</v>
+      </c>
+      <c r="D56" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="E56" s="24" t="s">
+        <v>93</v>
+      </c>
+      <c r="F56" s="38" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="B57" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="C57" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D57" s="29" t="s">
-        <v>131</v>
-      </c>
-      <c r="E57" s="30" t="s">
+      <c r="A57" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="C57" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="F57" s="29" t="s">
-        <v>32</v>
+      <c r="D57" s="26" t="s">
+        <v>63</v>
+      </c>
+      <c r="E57" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="F57" s="26" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="B58" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="C58" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="D58" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="E58" s="30" t="s">
+      <c r="A58" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B58" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="C58" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="F58" s="29" t="s">
-        <v>117</v>
+      <c r="D58" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="E58" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="F58" s="26" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="B59" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C59" s="31" t="s">
+      <c r="B59" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="C59" s="28" t="s">
         <v>8</v>
       </c>
       <c r="D59" s="29" t="s">
-        <v>31</v>
+        <v>130</v>
       </c>
       <c r="E59" s="30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F59" s="29" t="s">
         <v>32</v>
@@ -2454,16 +2511,16 @@
         <v>7</v>
       </c>
       <c r="C60" s="31" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="D60" s="29" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="E60" s="30" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F60" s="29" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
@@ -2471,139 +2528,199 @@
         <v>57</v>
       </c>
       <c r="B61" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="C61" s="31" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="29" t="s">
+        <v>31</v>
+      </c>
+      <c r="E61" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="F61" s="29" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B62" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D62" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="E62" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="F62" s="29" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="B63" s="42" t="s">
+        <v>7</v>
+      </c>
+      <c r="C63" s="42" t="s">
+        <v>44</v>
+      </c>
+      <c r="D63" s="43" t="s">
+        <v>152</v>
+      </c>
+      <c r="E63" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="F63" s="45" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="B64" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="C61" s="31" t="s">
-        <v>95</v>
-      </c>
-      <c r="D61" s="29" t="s">
+      <c r="C64" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="D64" s="29" t="s">
         <v>60</v>
       </c>
-      <c r="E61" s="30" t="s">
-        <v>95</v>
-      </c>
-      <c r="F61" s="29" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="B62" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C62" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D62" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="E62" s="16" t="s">
+      <c r="E64" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="F62" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="B63" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D63" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="E63" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="F63" s="11" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="15" t="s">
-        <v>132</v>
-      </c>
-      <c r="B64" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="C64" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D64" s="11" t="s">
-        <v>149</v>
-      </c>
-      <c r="E64" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="F64" s="11" t="s">
-        <v>134</v>
+      <c r="F64" s="29" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="B65" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="E65" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F65" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="B66" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E66" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F66" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="C67" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D67" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="E67" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F67" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="B68" s="15" t="s">
         <v>139</v>
       </c>
-      <c r="B65" s="15" t="s">
+      <c r="C68" s="15" t="s">
+        <v>44</v>
+      </c>
+      <c r="D68" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="C65" s="15" t="s">
+      <c r="E68" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F68" s="11" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="32" t="s">
+        <v>138</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C69" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D65" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="E65" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="F65" s="11" t="s">
+      <c r="D69" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E69" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="32" t="s">
+        <v>138</v>
+      </c>
+      <c r="B70" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D70" s="40" t="s">
         <v>142</v>
       </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="32" t="s">
-        <v>139</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C66" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E66" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="32" t="s">
-        <v>139</v>
-      </c>
-      <c r="B67" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C67" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D67" s="40" t="s">
+      <c r="E70" s="18" t="s">
+        <v>93</v>
+      </c>
+      <c r="F70" s="40" t="s">
         <v>143</v>
-      </c>
-      <c r="E67" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="F67" s="40" t="s">
-        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/data/projects.xlsx
+++ b/data/projects.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="401" uniqueCount="155">
   <si>
     <t>Allocation</t>
   </si>
@@ -362,9 +362,6 @@
     <t>IBFT &amp; UBPS Workflow Change</t>
   </si>
   <si>
-    <t>Afzal / Adnan</t>
-  </si>
-  <si>
     <t>Raast QR Upload</t>
   </si>
   <si>
@@ -431,18 +428,12 @@
     <t>Punjab Health commission</t>
   </si>
   <si>
-    <t>API Shared</t>
-  </si>
-  <si>
     <t>Payment Portal-Back Office - Raast Bulk/SPHF</t>
   </si>
   <si>
     <t>Both</t>
   </si>
   <si>
-    <t>Zohaib Shahzad</t>
-  </si>
-  <si>
     <t xml:space="preserve">Payment </t>
   </si>
   <si>
@@ -479,9 +470,6 @@
     <t>Paysys is working on it</t>
   </si>
   <si>
-    <t>Title fetch while re attempting</t>
-  </si>
-  <si>
     <t>BISE DI Khan</t>
   </si>
   <si>
@@ -489,6 +477,18 @@
   </si>
   <si>
     <t>UAT Done, CMC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zohaib / Mubashir </t>
+  </si>
+  <si>
+    <t>UAT Complete. Circular Awaited</t>
+  </si>
+  <si>
+    <t>IBFT Title Fetch with Actual Amount</t>
+  </si>
+  <si>
+    <t>Live</t>
   </si>
 </sst>
 </file>
@@ -527,7 +527,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -566,12 +566,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -596,12 +590,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="-0.249977111117893"/>
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -659,11 +665,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -671,25 +690,21 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -699,43 +714,67 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="14" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="11" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="13" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1315,31 +1354,31 @@
   <dimension ref="A1:F70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="51.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19.42578125" style="19" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" style="17" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="192.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="34" t="s">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="34" t="s">
+      <c r="B1" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="34" t="s">
+      <c r="C1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="34" t="s">
+      <c r="D1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="28" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1356,11 +1395,11 @@
       <c r="D2" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="E2" s="8" t="s">
         <v>93</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -1376,7 +1415,7 @@
       <c r="D3" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="8" t="s">
         <v>93</v>
       </c>
       <c r="F3" s="4" t="s">
@@ -1396,7 +1435,7 @@
       <c r="D4" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="16" t="s">
         <v>93</v>
       </c>
       <c r="F4" s="2" t="s">
@@ -1411,12 +1450,12 @@
         <v>27</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>44</v>
+        <v>8</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E5" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="E5" s="8" t="s">
         <v>93</v>
       </c>
       <c r="F5" s="2" t="s">
@@ -1436,7 +1475,7 @@
       <c r="D6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="8" t="s">
         <v>93</v>
       </c>
       <c r="F6" s="2" t="s">
@@ -1444,43 +1483,43 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="41" t="s">
         <v>57</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="41" t="s">
         <v>44</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="41" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="F7" s="36" t="s">
+      <c r="E7" s="42" t="s">
+        <v>93</v>
+      </c>
+      <c r="F7" s="43" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>126</v>
-      </c>
-      <c r="E8" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>127</v>
+      <c r="A8" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -1493,14 +1532,14 @@
       <c r="C9" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>115</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>118</v>
+      <c r="D9" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -1513,74 +1552,74 @@
       <c r="C10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D10" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="D10" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" s="52" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="51" t="s">
         <v>6</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>16</v>
+      <c r="D11" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="E11" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="15" t="s">
-        <v>8</v>
+      <c r="B12" s="30" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>80</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="E12" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="12" t="s">
         <v>93</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="37" t="s">
+      <c r="A13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B13" s="37" t="s">
-        <v>84</v>
+      <c r="B13" s="5" t="s">
+        <v>7</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="D13" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F13" s="12" t="s">
-        <v>154</v>
+        <v>18</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -1593,14 +1632,14 @@
       <c r="C14" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D14" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>153</v>
+      <c r="D14" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -1613,14 +1652,14 @@
       <c r="C15" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D15" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>67</v>
+      <c r="D15" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -1633,14 +1672,14 @@
       <c r="C16" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D16" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>66</v>
+      <c r="D16" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -1653,14 +1692,14 @@
       <c r="C17" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="12" t="s">
-        <v>91</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>95</v>
+      <c r="D17" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1673,94 +1712,94 @@
       <c r="C18" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>96</v>
+      <c r="D18" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="12">
+        <v>46218</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="5" t="s">
+      <c r="B19" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="D19" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E19" s="13">
+      <c r="D19" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="E20" s="12">
         <v>46218</v>
       </c>
-      <c r="F19" s="12" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="37" t="s">
-        <v>6</v>
-      </c>
-      <c r="B20" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="D20" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>73</v>
+      <c r="F20" s="11" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="5" t="s">
+      <c r="B21" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="D21" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="E21" s="13">
-        <v>46218</v>
-      </c>
-      <c r="F21" s="12" t="s">
-        <v>22</v>
+      <c r="D21" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E21" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="F21" s="27" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B22" s="37" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="37" t="s">
+      <c r="B22" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="F22" s="33" t="s">
-        <v>73</v>
+      <c r="D22" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E22" s="12">
+        <v>46220</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1773,14 +1812,14 @@
       <c r="C23" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E23" s="13">
-        <v>46220</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>24</v>
+      <c r="D23" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E23" s="12">
+        <v>46176</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1791,159 +1830,159 @@
         <v>7</v>
       </c>
       <c r="C24" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E24" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D24" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24" s="13">
-        <v>46176</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="7" t="s">
+      <c r="D26" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E26" s="15">
+        <v>46241</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B27" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="C26" s="7" t="s">
+      <c r="C27" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D26" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E26" s="17">
-        <v>46241</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+      <c r="D27" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="E27" s="15">
+        <v>46261</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B27" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" s="7" t="s">
+      <c r="B28" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D27" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="E27" s="17">
-        <v>46261</v>
-      </c>
-      <c r="F27" s="8" t="s">
+      <c r="D28" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E28" s="15">
+        <v>46227</v>
+      </c>
+      <c r="F28" s="7" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="7" t="s">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="7" t="s">
+      <c r="C29" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D28" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="E28" s="17">
-        <v>46227</v>
-      </c>
-      <c r="F28" s="8" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="41" t="s">
+      <c r="D30" s="39" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="40">
+        <v>46147</v>
+      </c>
+      <c r="F30" s="39" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B29" s="42" t="s">
+      <c r="B31" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="D29" s="43" t="s">
-        <v>149</v>
-      </c>
-      <c r="E29" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="F29" s="45" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="41" t="s">
-        <v>34</v>
-      </c>
-      <c r="B30" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="C30" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="D30" s="43" t="s">
-        <v>151</v>
-      </c>
-      <c r="E30" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="F30" s="45" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="B31" s="20" t="s">
-        <v>27</v>
-      </c>
-      <c r="C31" s="20" t="s">
-        <v>8</v>
+      <c r="C31" s="1" t="s">
+        <v>18</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>93</v>
+        <v>35</v>
+      </c>
+      <c r="E31" s="16">
+        <v>46318</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>34</v>
       </c>
@@ -1954,13 +1993,13 @@
         <v>18</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E32" s="18">
-        <v>46318</v>
+        <v>72</v>
+      </c>
+      <c r="E32" s="16">
+        <v>46125</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -1971,16 +2010,16 @@
         <v>27</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>80</v>
+        <v>18</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>93</v>
+        <v>36</v>
+      </c>
+      <c r="E33" s="16">
+        <v>46276</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>37</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -1994,16 +2033,16 @@
         <v>18</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="E34" s="18">
-        <v>46125</v>
+        <v>71</v>
+      </c>
+      <c r="E34" s="16">
+        <v>46161</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" s="10" customFormat="1" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>34</v>
       </c>
@@ -2014,713 +2053,713 @@
         <v>18</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E35" s="18">
-        <v>46276</v>
+        <v>42</v>
+      </c>
+      <c r="E35" s="16">
+        <v>46122</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>92</v>
+        <v>43</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
+      <c r="A36" s="18" t="s">
         <v>34</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="18" t="s">
+        <v>94</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E37" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="53" t="s">
+        <v>65</v>
+      </c>
+      <c r="B38" s="53" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" s="53" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38" s="54" t="s">
+        <v>143</v>
+      </c>
+      <c r="E38" s="55" t="s">
+        <v>93</v>
+      </c>
+      <c r="F38" s="54" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B39" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>111</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="F39" s="20" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B40" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>109</v>
+      </c>
+      <c r="E40" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B41" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D41" s="20" t="s">
+        <v>110</v>
+      </c>
+      <c r="E41" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="F41" s="20" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B42" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C42" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="D42" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="E42" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B43" s="58" t="s">
+        <v>27</v>
+      </c>
+      <c r="C43" s="58" t="s">
         <v>18</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="E36" s="18">
+      <c r="D43" s="56" t="s">
+        <v>153</v>
+      </c>
+      <c r="E43" s="57">
+        <v>46318</v>
+      </c>
+      <c r="F43" s="59" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B44" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C44" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="E44" s="21">
+        <v>46059</v>
+      </c>
+      <c r="F44" s="20" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B45" s="19" t="s">
+        <v>38</v>
+      </c>
+      <c r="C45" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D45" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="E45" s="21">
+        <v>46181</v>
+      </c>
+      <c r="F45" s="20" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B46" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C46" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D46" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E46" s="21">
+        <v>46227</v>
+      </c>
+      <c r="F46" s="20" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B47" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C47" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="D47" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="E47" s="21">
         <v>46161</v>
       </c>
-      <c r="F36" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B37" s="1" t="s">
+      <c r="F47" s="20" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B48" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C48" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E37" s="18">
-        <v>46147</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B38" s="1" t="s">
+      <c r="D48" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="E48" s="21">
+        <v>46181</v>
+      </c>
+      <c r="F48" s="20" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B49" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="C38" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E38" s="18">
-        <v>46122</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="B39" s="20" t="s">
+      <c r="C49" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D49" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="E49" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F49" s="20" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B50" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="19" t="s">
+        <v>94</v>
+      </c>
+      <c r="D50" s="20" t="s">
+        <v>104</v>
+      </c>
+      <c r="E50" s="21" t="s">
+        <v>94</v>
+      </c>
+      <c r="F50" s="20" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" s="50" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="B51" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="C39" s="20" t="s">
+      <c r="C51" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D39" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="E39" s="18" t="s">
+      <c r="D51" s="20" t="s">
+        <v>106</v>
+      </c>
+      <c r="E51" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F51" s="20" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="B40" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C40" s="1" t="s">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B52" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C52" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="D52" s="31" t="s">
+        <v>82</v>
+      </c>
+      <c r="E52" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F52" s="31" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C53" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D53" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="E53" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F53" s="31" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B54" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C54" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D54" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E54" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="F54" s="31" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B55" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55" s="23" t="s">
         <v>94</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E40" s="18" t="s">
+      <c r="D55" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="E55" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="F40" s="2" t="s">
+      <c r="F55" s="24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B56" s="23" t="s">
+        <v>103</v>
+      </c>
+      <c r="C56" s="23" t="s">
+        <v>94</v>
+      </c>
+      <c r="D56" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="E56" s="25" t="s">
+        <v>94</v>
+      </c>
+      <c r="F56" s="24" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="B41" s="15" t="s">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="B57" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C57" s="41" t="s">
+        <v>44</v>
+      </c>
+      <c r="D57" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="E57" s="42" t="s">
+        <v>93</v>
+      </c>
+      <c r="F57" s="43" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="B58" s="46" t="s">
+        <v>7</v>
+      </c>
+      <c r="C58" s="46" t="s">
+        <v>44</v>
+      </c>
+      <c r="D58" s="47" t="s">
+        <v>148</v>
+      </c>
+      <c r="E58" s="48" t="s">
+        <v>93</v>
+      </c>
+      <c r="F58" s="49" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="B59" s="44" t="s">
         <v>27</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C59" s="44" t="s">
+        <v>8</v>
+      </c>
+      <c r="D59" s="43" t="s">
+        <v>129</v>
+      </c>
+      <c r="E59" s="42" t="s">
+        <v>93</v>
+      </c>
+      <c r="F59" s="43" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="B60" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="C60" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="D60" s="43" t="s">
+        <v>56</v>
+      </c>
+      <c r="E60" s="42" t="s">
+        <v>93</v>
+      </c>
+      <c r="F60" s="43" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="B61" s="41" t="s">
+        <v>28</v>
+      </c>
+      <c r="C61" s="41" t="s">
+        <v>8</v>
+      </c>
+      <c r="D61" s="43" t="s">
+        <v>31</v>
+      </c>
+      <c r="E61" s="42" t="s">
+        <v>93</v>
+      </c>
+      <c r="F61" s="43" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="B62" s="41" t="s">
+        <v>27</v>
+      </c>
+      <c r="C62" s="41" t="s">
+        <v>94</v>
+      </c>
+      <c r="D62" s="43" t="s">
+        <v>60</v>
+      </c>
+      <c r="E62" s="42" t="s">
+        <v>94</v>
+      </c>
+      <c r="F62" s="43" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B63" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="C63" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="E63" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="F63" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B64" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="13" t="s">
+        <v>8</v>
+      </c>
+      <c r="D64" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="E64" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="F64" s="10" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="B65" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C65" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D65" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="E65" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="F65" s="10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="B66" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D66" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="E66" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="F66" s="10" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E67" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="B68" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D68" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="E68" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F68" s="33" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="B69" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="C69" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="D69" s="36" t="s">
         <v>146</v>
       </c>
-      <c r="E41" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="F41" s="11" t="s">
+      <c r="E69" s="37" t="s">
+        <v>93</v>
+      </c>
+      <c r="F69" s="38" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B42" s="21" t="s">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="26" t="s">
+        <v>151</v>
+      </c>
+      <c r="B70" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="C42" s="21" t="s">
-        <v>44</v>
-      </c>
-      <c r="D42" s="22" t="s">
-        <v>111</v>
-      </c>
-      <c r="E42" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="F42" s="22" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B43" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C43" s="21" t="s">
+      <c r="C70" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D43" s="22" t="s">
-        <v>109</v>
-      </c>
-      <c r="E43" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="F43" s="22" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B44" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C44" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="22" t="s">
-        <v>110</v>
-      </c>
-      <c r="E44" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="F44" s="22" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B45" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C45" s="21" t="s">
-        <v>14</v>
-      </c>
-      <c r="D45" s="22" t="s">
-        <v>46</v>
-      </c>
-      <c r="E45" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="F45" s="22" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B46" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C46" s="21" t="s">
-        <v>80</v>
-      </c>
-      <c r="D46" s="22" t="s">
-        <v>45</v>
-      </c>
-      <c r="E46" s="23" t="s">
-        <v>93</v>
-      </c>
-      <c r="F46" s="22" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B47" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C47" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D47" s="22" t="s">
-        <v>48</v>
-      </c>
-      <c r="E47" s="23">
-        <v>46059</v>
-      </c>
-      <c r="F47" s="22" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B48" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C48" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D48" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="E48" s="23">
-        <v>46181</v>
-      </c>
-      <c r="F48" s="22" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B49" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C49" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D49" s="22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E49" s="23">
-        <v>46227</v>
-      </c>
-      <c r="F49" s="22" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B50" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C50" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D50" s="22" t="s">
-        <v>52</v>
-      </c>
-      <c r="E50" s="23">
-        <v>46161</v>
-      </c>
-      <c r="F50" s="22" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B51" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C51" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="D51" s="22" t="s">
-        <v>53</v>
-      </c>
-      <c r="E51" s="23">
-        <v>46181</v>
-      </c>
-      <c r="F51" s="22" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B52" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C52" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="D52" s="22" t="s">
-        <v>136</v>
-      </c>
-      <c r="E52" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="F52" s="22" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B53" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="C53" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="D53" s="22" t="s">
-        <v>104</v>
-      </c>
-      <c r="E53" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="F53" s="22" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B54" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C54" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="D54" s="22" t="s">
-        <v>106</v>
-      </c>
-      <c r="E54" s="23" t="s">
-        <v>94</v>
-      </c>
-      <c r="F54" s="22" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="B55" s="39" t="s">
-        <v>81</v>
-      </c>
-      <c r="C55" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D55" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="E55" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="F55" s="38" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="B56" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C56" s="25" t="s">
-        <v>14</v>
-      </c>
-      <c r="D56" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="E56" s="24" t="s">
-        <v>93</v>
-      </c>
-      <c r="F56" s="38" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="B57" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="C57" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="D57" s="26" t="s">
-        <v>63</v>
-      </c>
-      <c r="E57" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="F57" s="26" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="B58" s="25" t="s">
-        <v>103</v>
-      </c>
-      <c r="C58" s="25" t="s">
-        <v>94</v>
-      </c>
-      <c r="D58" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="E58" s="27" t="s">
-        <v>94</v>
-      </c>
-      <c r="F58" s="26" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="B59" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="C59" s="28" t="s">
-        <v>8</v>
-      </c>
-      <c r="D59" s="29" t="s">
-        <v>130</v>
-      </c>
-      <c r="E59" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="F59" s="29" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="B60" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="C60" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="29" t="s">
-        <v>56</v>
-      </c>
-      <c r="E60" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="F60" s="29" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="B61" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="C61" s="31" t="s">
-        <v>8</v>
-      </c>
-      <c r="D61" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="E61" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="F61" s="29" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="B62" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="C62" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="D62" s="29" t="s">
-        <v>74</v>
-      </c>
-      <c r="E62" s="30" t="s">
-        <v>93</v>
-      </c>
-      <c r="F62" s="29" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="41" t="s">
-        <v>57</v>
-      </c>
-      <c r="B63" s="42" t="s">
-        <v>7</v>
-      </c>
-      <c r="C63" s="42" t="s">
-        <v>44</v>
-      </c>
-      <c r="D63" s="43" t="s">
-        <v>152</v>
-      </c>
-      <c r="E63" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="F63" s="45" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="B64" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="C64" s="31" t="s">
-        <v>94</v>
-      </c>
-      <c r="D64" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="E64" s="30" t="s">
-        <v>94</v>
-      </c>
-      <c r="F64" s="29" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="B65" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="C65" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D65" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="E65" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="F65" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="B66" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C66" s="15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D66" s="11" t="s">
-        <v>134</v>
-      </c>
-      <c r="E66" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="F66" s="11" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="B67" s="15" t="s">
-        <v>137</v>
-      </c>
-      <c r="C67" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D67" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="E67" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="F67" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="15" t="s">
-        <v>138</v>
-      </c>
-      <c r="B68" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="C68" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D68" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="E68" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="F68" s="11" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C69" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="E69" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="B70" s="32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="D70" s="40" t="s">
-        <v>142</v>
-      </c>
-      <c r="E70" s="18" t="s">
-        <v>93</v>
-      </c>
-      <c r="F70" s="40" t="s">
-        <v>143</v>
+      <c r="D70" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E70" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
